--- a/outputs/tables/00_关键结果汇总.xlsx
+++ b/outputs/tables/00_关键结果汇总.xlsx
@@ -1188,19 +1188,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>22086, 22952</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>22910</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>22086, 22952</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.0117</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2427</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>16.1137</v>
@@ -1209,16 +1209,16 @@
         <v>0.011</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3007</v>
+        <v>4.3189</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>PAPER CHAIN KIT 50'S CHR &amp; 60 CAKE CASES VINTAGE CH</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t xml:space="preserve">PAPER CHAIN KIT VINTAGE </t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>PAPER CHAIN KIT 50'S CHR &amp; 60 CAKE CASES VINTAGE CH</t>
         </is>
       </c>
     </row>
@@ -1228,19 +1228,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>22910</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>22086, 22952</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>22910</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.0117</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.2427</v>
       </c>
       <c r="F3" t="n">
         <v>16.1137</v>
@@ -1249,16 +1249,16 @@
         <v>0.011</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3189</v>
+        <v>1.3007</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t xml:space="preserve">PAPER CHAIN KIT VINTAGE </t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>PAPER CHAIN KIT 50'S CHR &amp; 60 CAKE CASES VINTAGE CH</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PAPER CHAIN KIT VINTAGE </t>
         </is>
       </c>
     </row>
@@ -1508,19 +1508,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>22726</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>22727</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>22726</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.029</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6152</v>
+        <v>0.6523</v>
       </c>
       <c r="F10" t="n">
         <v>13.8468</v>
@@ -1529,16 +1529,16 @@
         <v>0.0269</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4831</v>
+        <v>2.7405</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>ALARM CLOCK BAKELIKE GRE</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>ALARM CLOCK BAKELIKE RED</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ALARM CLOCK BAKELIKE GRE</t>
         </is>
       </c>
     </row>
@@ -1548,19 +1548,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>22727</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>22726</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>22727</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.029</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6523</v>
+        <v>0.6152</v>
       </c>
       <c r="F11" t="n">
         <v>13.8468</v>
@@ -1569,16 +1569,16 @@
         <v>0.0269</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7405</v>
+        <v>2.4831</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>ALARM CLOCK BAKELIKE RED</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>ALARM CLOCK BAKELIKE GRE</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ALARM CLOCK BAKELIKE RED</t>
         </is>
       </c>
     </row>
@@ -1588,19 +1588,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>20728, 22356</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>20723</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>20728, 22356</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.0116</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2298</v>
+        <v>0.6791</v>
       </c>
       <c r="F12" t="n">
         <v>13.4329</v>
@@ -1609,16 +1609,16 @@
         <v>0.0108</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2761</v>
+        <v>2.9587</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>LUNCH BAG CARS BLUE &amp; CHARLOTTE BAG PINK POLKA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>STRAWBERRY CHARLOTTE BAG</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>LUNCH BAG CARS BLUE &amp; CHARLOTTE BAG PINK POLKA</t>
         </is>
       </c>
     </row>
@@ -1628,19 +1628,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>20723</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>20728, 22356</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>20723</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.0116</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6791</v>
+        <v>0.2298</v>
       </c>
       <c r="F13" t="n">
         <v>13.4329</v>
@@ -1649,16 +1649,16 @@
         <v>0.0108</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9587</v>
+        <v>1.2761</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>STRAWBERRY CHARLOTTE BAG</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>LUNCH BAG CARS BLUE &amp; CHARLOTTE BAG PINK POLKA</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>STRAWBERRY CHARLOTTE BAG</t>
         </is>
       </c>
     </row>
@@ -1668,19 +1668,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>20724, 20728</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>20723</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>20724, 20728</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.0129</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2551</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="F14" t="n">
         <v>13.4081</v>
@@ -1689,16 +1689,16 @@
         <v>0.0119</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3168</v>
+        <v>2.9472</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>RED RETROSPOT CHARLOTTE  &amp; LUNCH BAG CARS BLUE</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>STRAWBERRY CHARLOTTE BAG</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>RED RETROSPOT CHARLOTTE  &amp; LUNCH BAG CARS BLUE</t>
         </is>
       </c>
     </row>
@@ -1708,19 +1708,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>20723</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>20724, 20728</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>20723</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.0129</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.2551</v>
       </c>
       <c r="F15" t="n">
         <v>13.4081</v>
@@ -1729,16 +1729,16 @@
         <v>0.0119</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9472</v>
+        <v>1.3168</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>STRAWBERRY CHARLOTTE BAG</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>RED RETROSPOT CHARLOTTE  &amp; LUNCH BAG CARS BLUE</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>STRAWBERRY CHARLOTTE BAG</t>
         </is>
       </c>
     </row>

--- a/outputs/tables/00_关键结果汇总.xlsx
+++ b/outputs/tables/00_关键结果汇总.xlsx
@@ -22,10 +22,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_波士顿矩阵" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_KMeans画像" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_复购漏斗" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_预测回测" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_未来30天预测" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_图表索引" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_大屏组件" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12b_阈值稳健性" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_预测回测" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_未来30天预测" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_图表索引" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_大屏组件" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_说明'!$A$1:$B$11</definedName>
@@ -43,10 +44,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'10_波士顿矩阵'!$A$1:$K$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'11_KMeans画像'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'12_复购漏斗'!$A$1:$D$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'13_预测回测'!$A$1:$D$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'14_未来30天预测'!$A$1:$E$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'15_图表索引'!$A$1:$E$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'16_大屏组件'!$A$1:$C$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'12b_阈值稳健性'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'13_预测回测'!$A$1:$D$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'14_未来30天预测'!$A$1:$E$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'15_图表索引'!$A$1:$E$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'16_大屏组件'!$A$1:$C$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2808,6 +2810,163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13.2" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="14.8" customWidth="1" min="3" max="3"/>
+    <col width="13.2" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="13.2" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>切分方式</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>阈值(R天/F次/M英镑)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>核心高价值客户数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>人数占比(%)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>核心客户营收(英镑)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>营收占比(%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>M高组人数</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>M高组营收占比(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>中位数（采用）</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>203 / 2.00 / 488.69</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1069</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3467511.14</v>
+      </c>
+      <c r="F2" t="n">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1863</v>
+      </c>
+      <c r="H2" t="n">
+        <v>90.66</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>均值</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>249 / 2.89 / 1329.56</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>572</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3043082.8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>61.43</v>
+      </c>
+      <c r="G3" t="n">
+        <v>762</v>
+      </c>
+      <c r="H3" t="n">
+        <v>72.45</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>60 分位</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>126 / 2.00 / 671.73</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>784</v>
+      </c>
+      <c r="D4" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3113042.61</v>
+      </c>
+      <c r="F4" t="n">
+        <v>62.84</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1491</v>
+      </c>
+      <c r="H4" t="n">
+        <v>86.34999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3925,7 +4084,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4484,7 +4643,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5474,343 +5633,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E36"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="29.2" customWidth="1" min="1" max="1"/>
-    <col width="21.2" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>组件</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>栅格宽度</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>tab1_trend</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>月度销售额趋势</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>tab1_dual</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>销售额 × 订单数双轴</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>tab1_country_bar</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TOP10 国家销售额</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>tab1_timeline</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>月度国家排名时间轴</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>tab1_heatmap</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>星期时段热力图</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>tab2_rfm_pie</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>RFM 金额贡献玫瑰图</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>tab2_rfm_bar</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>RFM 客群规模与贡献</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>tab2_cohort</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>同期群留存曲线</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>tab2_funnel</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>复购漏斗</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>tab2_kmeans</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>K-Means 分群画像</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>tab3_top_products</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TOP10 热销商品</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>tab3_cat_pie</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>品类结构环形图</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>tab3_wordcloud</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>热销商品词云</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>tab3_abc</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ABC 分类贡献</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>tab3_rules</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>关联规则 Lift 排行</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>tab3_table</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>商品明细表</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>tab4_forecast</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>预测与置信区间</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>tab4_backtest</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>回测对比</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>tab4_yoy</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>同比增速复盘</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>tab4_bcg</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>波士顿矩阵</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6044,6 +5866,343 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:B20"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29.2" customWidth="1" min="1" max="1"/>
+    <col width="21.2" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>组件</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>栅格宽度</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tab1_trend</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>月度销售额趋势</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tab1_dual</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>销售额 × 订单数双轴</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tab1_country_bar</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TOP10 国家销售额</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tab1_timeline</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>月度国家排名时间轴</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tab1_heatmap</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>星期时段热力图</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tab2_rfm_pie</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RFM 金额贡献玫瑰图</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tab2_rfm_bar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RFM 客群规模与贡献</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tab2_cohort</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>同期群留存曲线</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tab2_funnel</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>复购漏斗</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tab2_kmeans</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>K-Means 分群画像</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tab3_top_products</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TOP10 热销商品</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tab3_cat_pie</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>品类结构环形图</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tab3_wordcloud</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>热销商品词云</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tab3_abc</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ABC 分类贡献</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tab3_rules</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>关联规则 Lift 排行</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tab3_table</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>商品明细表</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tab4_forecast</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>预测与置信区间</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tab4_backtest</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>回测对比</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tab4_yoy</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>同比增速复盘</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tab4_bcg</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>波士顿矩阵</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/outputs/tables/00_关键结果汇总.xlsx
+++ b/outputs/tables/00_关键结果汇总.xlsx
@@ -20,13 +20,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_帕累托ABC" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_关联规则Top20" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_波士顿矩阵" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_KMeans画像" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_复购漏斗" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12b_阈值稳健性" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_预测回测" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_未来30天预测" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_图表索引" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_大屏组件" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10b_增速稳健性" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_KMeans画像" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11b_聚类预处理消融" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11c_聚类选型与稳定性" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_复购漏斗" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12b_阈值稳健性" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_预测回测" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_未来30天预测" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_图表索引" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_大屏组件" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_说明'!$A$1:$B$11</definedName>
@@ -41,14 +44,17 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'07c_平均留存曲线'!$A$1:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'08_帕累托ABC'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'09_关联规则Top20'!$A$1:$J$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'10_波士顿矩阵'!$A$1:$K$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'11_KMeans画像'!$A$1:$I$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'12_复购漏斗'!$A$1:$D$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'12b_阈值稳健性'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'13_预测回测'!$A$1:$D$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'14_未来30天预测'!$A$1:$E$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'15_图表索引'!$A$1:$E$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'16_大屏组件'!$A$1:$C$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'10_波士顿矩阵'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'10b_增速稳健性'!$A$1:$P$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'11_KMeans画像'!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'11b_聚类预处理消融'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'11c_聚类选型与稳定性'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'12_复购漏斗'!$A$1:$D$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'12b_阈值稳健性'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'13_预测回测'!$A$1:$D$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'14_未来30天预测'!$A$1:$E$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'15_图表索引'!$A$1:$E$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'16_大屏组件'!$A$1:$C$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1996,7 +2002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35.6" customWidth="1" min="1" max="1"/>
@@ -2005,11 +2011,17 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="11.6" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="22.8" customWidth="1" min="7" max="7"/>
-    <col width="16.4" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="29.2" customWidth="1" min="10" max="10"/>
-    <col width="21.2" customWidth="1" min="11" max="11"/>
+    <col width="24.4" customWidth="1" min="7" max="7"/>
+    <col width="13.2" customWidth="1" min="8" max="8"/>
+    <col width="11.6" customWidth="1" min="9" max="9"/>
+    <col width="27.6" customWidth="1" min="10" max="10"/>
+    <col width="14.8" customWidth="1" min="11" max="11"/>
+    <col width="16.4" customWidth="1" min="12" max="12"/>
+    <col width="22.8" customWidth="1" min="13" max="13"/>
+    <col width="16.4" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="29.2" customWidth="1" min="16" max="16"/>
+    <col width="21.2" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2045,25 +2057,55 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>TrendAnnualPct</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>TrendR2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TrendT</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TrendSignificant</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>N_Months</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>MonthlyCV</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>RelativeShare</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ShareFlag</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>GrowthFlag</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Quadrant</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>RevenueShare</t>
         </is>
@@ -2091,24 +2133,42 @@
         <v>1236</v>
       </c>
       <c r="G2" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>24</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="M2" t="n">
         <v>3.309</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>金牛 Cash Cows</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="Q2" t="n">
         <v>24.86</v>
       </c>
     </row>
@@ -2134,24 +2194,42 @@
         <v>631</v>
       </c>
       <c r="G3" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>24</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M3" t="n">
         <v>2.335</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>金牛 Cash Cows</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="Q3" t="n">
         <v>18.93</v>
       </c>
     </row>
@@ -2177,24 +2255,42 @@
         <v>364</v>
       </c>
       <c r="G4" t="n">
+        <v>37.53</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>24</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="M4" t="n">
         <v>2.164</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>明星 Stars</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="Q4" t="n">
         <v>17.79</v>
       </c>
     </row>
@@ -2220,24 +2316,42 @@
         <v>635</v>
       </c>
       <c r="G5" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="M5" t="n">
         <v>1.683</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>明星 Stars</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="Q5" t="n">
         <v>14.41</v>
       </c>
     </row>
@@ -2263,24 +2377,42 @@
         <v>548</v>
       </c>
       <c r="G6" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>24</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="M6" t="n">
         <v>0.884</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>瘦狗 Dogs</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="Q6" t="n">
         <v>8.119999999999999</v>
       </c>
     </row>
@@ -2306,24 +2438,42 @@
         <v>273</v>
       </c>
       <c r="G7" t="n">
+        <v>155.26</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>24</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="M7" t="n">
         <v>0.614</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>问题 Question Marks</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="Q7" t="n">
         <v>5.78</v>
       </c>
     </row>
@@ -2349,24 +2499,42 @@
         <v>66</v>
       </c>
       <c r="G8" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>24</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="M8" t="n">
         <v>0.317</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>问题 Question Marks</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="Q8" t="n">
         <v>3.07</v>
       </c>
     </row>
@@ -2392,24 +2560,42 @@
         <v>262</v>
       </c>
       <c r="G9" t="n">
+        <v>-19.38</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>24</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="M9" t="n">
         <v>0.301</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>瘦狗 Dogs</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="Q9" t="n">
         <v>2.92</v>
       </c>
     </row>
@@ -2435,24 +2621,42 @@
         <v>107</v>
       </c>
       <c r="G10" t="n">
+        <v>36.34</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>24</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="M10" t="n">
         <v>0.231</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>问题 Question Marks</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="Q10" t="n">
         <v>2.26</v>
       </c>
     </row>
@@ -2478,24 +2682,42 @@
         <v>379</v>
       </c>
       <c r="G11" t="n">
+        <v>-32.85</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>24</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="M11" t="n">
         <v>0.132</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>瘦狗 Dogs</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="Q11" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -2521,34 +2743,871 @@
         <v>35</v>
       </c>
       <c r="G12" t="n">
+        <v>-5.92</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>24</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="M12" t="n">
         <v>0.055</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>瘦狗 Dogs</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="Q12" t="n">
         <v>0.55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K12"/>
+  <autoFilter ref="A1:Q12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35.6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="24.4" customWidth="1" min="4" max="4"/>
+    <col width="16.4" customWidth="1" min="5" max="5"/>
+    <col width="13.2" customWidth="1" min="6" max="6"/>
+    <col width="11.6" customWidth="1" min="7" max="7"/>
+    <col width="16.4" customWidth="1" min="8" max="8"/>
+    <col width="22.8" customWidth="1" min="9" max="9"/>
+    <col width="24.4" customWidth="1" min="10" max="10"/>
+    <col width="27.6" customWidth="1" min="11" max="11"/>
+    <col width="29.2" customWidth="1" min="12" max="12"/>
+    <col width="29.2" customWidth="1" min="13" max="13"/>
+    <col width="27.6" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="38.8" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ProductCategory</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue_Last12M</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>YoY_Growth</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>TrendAnnualPct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>GrowthGap</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>TrendR2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TrendT</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>MonthlyCV</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>RelativeShare</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>GrowthFlag_YoY</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>GrowthFlag_Trend</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Quadrant</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Quadrant_Trend</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TrendSignificant</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Consistent</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Party &amp; Occasion</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>90379.7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50.52</v>
+      </c>
+      <c r="D2" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>问题 Question Marks</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>问题 Question Marks</t>
+        </is>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>趋势显著（|t|≥临界值），象限归属可信</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Christmas &amp; Seasonal</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>170103.05</v>
+      </c>
+      <c r="C3" t="n">
+        <v>40.61</v>
+      </c>
+      <c r="D3" t="n">
+        <v>155.26</v>
+      </c>
+      <c r="E3" t="n">
+        <v>114.65</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>问题 Question Marks</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>问题 Question Marks</t>
+        </is>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>趋势不显著，增速主要为月度波动，象限归属待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bags &amp; Storage</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>523392.22</v>
+      </c>
+      <c r="C4" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="D4" t="n">
+        <v>37.53</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.164</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>明星 Stars</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>明星 Stars</t>
+        </is>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>趋势显著（|t|≥临界值），象限归属可信</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Toys &amp; Games</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>66366.21000000001</v>
+      </c>
+      <c r="C5" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="D5" t="n">
+        <v>36.34</v>
+      </c>
+      <c r="E5" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>问题 Question Marks</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>问题 Question Marks</t>
+        </is>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>趋势不显著，增速主要为月度波动，象限归属待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Home Decor &amp; Lighting</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>423842.03</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.683</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>明星 Stars</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>金牛 Cash Cows</t>
+        </is>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>不一致</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>趋势不显著，增速主要为月度波动，象限归属待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Other Household</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>731544.64</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="D7" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.309</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>金牛 Cash Cows</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>金牛 Cash Cows</t>
+        </is>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>趋势不显著，增速主要为月度波动，象限归属待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Stationery &amp; Wrap</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>239031.93</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="D8" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="E8" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>瘦狗 Dogs</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>瘦狗 Dogs</t>
+        </is>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>趋势不显著，增速主要为月度波动，象限归属待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>556942.0600000001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>金牛 Cash Cows</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>金牛 Cash Cows</t>
+        </is>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>趋势不显著，增速主要为月度波动，象限归属待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bath &amp; Fragrance</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>16173.58</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-5.92</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>瘦狗 Dogs</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>瘦狗 Dogs</t>
+        </is>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>趋势不显著，增速主要为月度波动，象限归属待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Garden &amp; Outdoor</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>86045.05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-29.77</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-19.38</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>瘦狗 Dogs</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>瘦狗 Dogs</t>
+        </is>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>趋势不显著，增速主要为月度波动，象限归属待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Jewellery &amp; Accessory</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>38371.62</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-48.27</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-32.85</v>
+      </c>
+      <c r="E12" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>瘦狗 Dogs</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>瘦狗 Dogs</t>
+        </is>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>趋势显著（|t|≥临界值），象限归属可信</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:P12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2617,28 +3676,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1215</v>
+        <v>1965</v>
       </c>
       <c r="C2" t="n">
-        <v>86.53</v>
+        <v>175.73</v>
       </c>
       <c r="D2" t="n">
-        <v>5.96</v>
+        <v>4.59</v>
       </c>
       <c r="E2" t="n">
-        <v>3197.9</v>
+        <v>2200.88</v>
       </c>
       <c r="F2" t="n">
-        <v>3885451.55</v>
+        <v>4324728.29</v>
       </c>
       <c r="G2" t="n">
-        <v>32.61</v>
+        <v>52.74</v>
       </c>
       <c r="H2" t="n">
-        <v>78.43000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2648,28 +3707,28 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1761</v>
+      </c>
+      <c r="C3" t="n">
+        <v>330.21</v>
+      </c>
+      <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
-        <v>2511</v>
-      </c>
-      <c r="C3" t="n">
-        <v>327.23</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.4</v>
-      </c>
       <c r="E3" t="n">
-        <v>425.53</v>
+        <v>357.31</v>
       </c>
       <c r="F3" t="n">
-        <v>1068505.22</v>
+        <v>629228.48</v>
       </c>
       <c r="G3" t="n">
-        <v>67.39</v>
+        <v>47.26</v>
       </c>
       <c r="H3" t="n">
-        <v>21.57</v>
+        <v>12.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2683,7 +3742,496 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32.40000000000001" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Preprocess</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PreprocessDesc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Silhouette</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>log1p_zscore</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>log1p + Z-score（对照口径：仅削弱量纲，未消除偏态）</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4271</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>log1p_zscore</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>log1p + Z-score（对照口径：仅削弱量纲，未消除偏态）</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3823</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>log1p_zscore</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>log1p + Z-score（对照口径：仅削弱量纲，未消除偏态）</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3632</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>log1p_zscore</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>log1p + Z-score（对照口径：仅削弱量纲，未消除偏态）</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.336</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>log1p_zscore</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>log1p + Z-score（对照口径：仅削弱量纲，未消除偏态）</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.298</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>winsor99_log_zscore</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>99% 缩尾 + log1p + Z-score</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4269</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>winsor99_log_zscore</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>99% 缩尾 + log1p + Z-score</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3836</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>winsor99_log_zscore</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>99% 缩尾 + log1p + Z-score</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3639</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>winsor99_log_zscore</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>99% 缩尾 + log1p + Z-score</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3008</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>winsor99_log_zscore</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>99% 缩尾 + log1p + Z-score</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3038</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>quantile_normal</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>分位数变换 → 正态分布（采用口径）</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.7412</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>quantile_normal</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>分位数变换 → 正态分布（采用口径）</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5261</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>quantile_normal</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>分位数变换 → 正态分布（采用口径）</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3444</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>quantile_normal</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>分位数变换 → 正态分布（采用口径）</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3391</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>quantile_normal</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>分位数变换 → 正态分布（采用口径）</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.3255</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D16"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="16.4" customWidth="1" min="2" max="2"/>
+    <col width="14.8" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="11.6" customWidth="1" min="5" max="5"/>
+    <col width="13.2" customWidth="1" min="6" max="6"/>
+    <col width="13.2" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Bootstrap</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ARI_Mean</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ARI_Median</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ARI_P5</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ARI_P95</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ARI_Min</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9748</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9383</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9953</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8872</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9552</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9619</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9127</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9822</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9058</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9337</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9395</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8783</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9779</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7936</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6451</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9473</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5386</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2804,7 +4352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2961,7 +4509,240 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>n_rows</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>302786</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>n_invoices</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11875</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>n_customers</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3726</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>n_products</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4507</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>n_countries</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>total_revenue_gbp</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5676066.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>avg_order_value_gbp</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>488.22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>date_range</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>['2009-12-01', '2011-11-30']</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>top_country</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>top_country_share</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>84.95999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>top_category</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Other Household</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>abc_counts</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{'C': 2593, 'B': 1334, 'A': 1135}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>abc_revenue_share</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>{'A': 80.0, 'B': 15.0, 'C': 5.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>repeat_purchase_rate</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>52.74</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>n_apriori_rules</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3866</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>best_forecast_model</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Holt-Winters</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cohort_m1_retention</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10.65</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cohort_m6_retention</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9.720000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>top1_customer_value_share</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>28.16</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B20"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4084,7 +5865,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4643,7 +6424,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5637,240 +7418,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>指标</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>n_rows</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>302786</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>n_invoices</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>11875</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>n_customers</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3726</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>n_products</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4507</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>n_countries</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>total_revenue_gbp</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5676066.77</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>avg_order_value_gbp</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>488.22</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>date_range</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>['2009-12-01', '2011-11-30']</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>top_country</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>top_country_share</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>84.95999999999999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>top_category</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Other Household</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>abc_counts</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'C': 2593, 'B': 1334, 'A': 1135}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>abc_revenue_share</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'A': 80.0, 'B': 15.0, 'C': 5.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>repeat_purchase_rate</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>52.74</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>n_apriori_rules</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3866</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>best_forecast_model</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Holt-Winters</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cohort_m1_retention</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>10.65</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cohort_m6_retention</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>9.720000000000001</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>top1_customer_value_share</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>28.16</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B20"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/outputs/tables/00_关键结果汇总.xlsx
+++ b/outputs/tables/00_关键结果汇总.xlsx
@@ -30,6 +30,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_未来30天预测" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_图表索引" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_大屏组件" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_流失预警窗口" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_流失预警模型对比" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_流失预警系数" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_流失预警十分位" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_流失预警分层AUC" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_流失预警多窗口" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_流失预警阈值ROI" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_流失预警名单" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_说明'!$A$1:$B$11</definedName>
@@ -55,6 +63,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'14_未来30天预测'!$A$1:$E$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'15_图表索引'!$A$1:$E$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'16_大屏组件'!$A$1:$C$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'17_流失预警窗口'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'18_流失预警模型对比'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'19_流失预警系数'!$A$1:$F$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'20_流失预警十分位'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'21_流失预警分层AUC'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'22_流失预警多窗口'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'23_流失预警阈值ROI'!$A$1:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'24_流失预警名单'!$A$1:$H$301</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7755,6 +7771,1374 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13.2" customWidth="1" min="1" max="1"/>
+    <col width="38.8" customWidth="1" min="2" max="2"/>
+    <col width="38.8" customWidth="1" min="3" max="3"/>
+    <col width="14.8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11.6" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>窗口</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>观测窗</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>表现窗</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>表现窗长度(天)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>基线客户数</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>流失人数</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>流失率(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>主建模窗口</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2009-12-01 ~ 2011-08-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2011-08-31 ~ 2011-11-30</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>91</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3255</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2416</v>
+      </c>
+      <c r="G2" t="n">
+        <v>74.22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>时间外验证窗口</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2009-12-01 ~ 2011-05-31</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2011-05-31 ~ 2011-08-31</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>92</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3016</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2413</v>
+      </c>
+      <c r="G3" t="n">
+        <v>80.01000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19.6" customWidth="1" min="1" max="1"/>
+    <col width="11.6" customWidth="1" min="2" max="2"/>
+    <col width="16.4" customWidth="1" min="3" max="3"/>
+    <col width="11.6" customWidth="1" min="4" max="4"/>
+    <col width="13.2" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="11.6" customWidth="1" min="7" max="7"/>
+    <col width="13.2" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>CV_AUC</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CV_PR_AUC</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>CV_KS</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>时间外_AUC</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>时间外_PR_AUC</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>时间外_KS</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>AUC衰减</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>逻辑回归</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.7241</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.8581</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7439</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.0199</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>随机森林</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7215</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8587</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7356</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8956</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.0142</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>集成 LR+RF 等权</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.7244</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8609</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24.4" customWidth="1" min="1" max="1"/>
+    <col width="29.2" customWidth="1" min="2" max="2"/>
+    <col width="13.2" customWidth="1" min="3" max="3"/>
+    <col width="11.6" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>特征</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>业务含义</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>系数(标准化)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>绝对值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>方向性检验</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SKUs</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>累计购买过的商品种类数</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.6338</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6338</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>抑制流失</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>与业务先验一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SKUperOrder</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>单次购买的商品种类数</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5518</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5518</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>推高流失</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>与业务先验一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Recency</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>距末次购买天数（观测窗末计）</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>推高流失</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>与业务先验一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>观测窗内购买次数</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.2172</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2172</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>抑制流失</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>与业务先验一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Monetary</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>观测窗内累计消费额</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.1719</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1719</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>抑制流失</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>与业务先验一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MonShare90</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>近 90 天消费额占历史比重</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.1643</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1643</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>抑制流失</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>与业务先验一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RecencyShare90</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>近 90 天购买次数占历史比重</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>推高流失</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>与业务先验一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cats</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>累计购买过的品类数</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.098</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>抑制流失</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>与业务先验一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SpanDays</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>首次至末次购买跨度</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>推高流失</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>与业务先验一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tenure</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>入会时长（距首次购买天数）</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>推高流失</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>系数近 0：与 Frequency/Tenure 共线，效应被吸收</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IsUK</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>是否英国客户（1=是）</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.0332</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0332</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>抑制流失</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>系数近 0：与 Frequency/Tenure 共线，效应被吸收</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AvgGap</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>平均购买间隔（入会时长 ÷ 次数）</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>抑制流失</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>系数近 0：与 Frequency/Tenure 共线，效应被吸收</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>客单价（消费额 ÷ 次数）</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>抑制流失</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>系数近 0：与 Frequency/Tenure 共线，效应被吸收</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HasReturn</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>历史是否发生退货（1=是）</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>抑制流失</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>系数近 0：与 Frequency/Tenure 共线，效应被吸收</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11.6" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14.8" customWidth="1" min="4" max="4"/>
+    <col width="30.8" customWidth="1" min="5" max="5"/>
+    <col width="13.2" customWidth="1" min="6" max="6"/>
+    <col width="16.4" customWidth="1" min="7" max="7"/>
+    <col width="14.8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decile</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>客户数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>实际流失数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>实际流失率(%)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>平均预测概率</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>提升度Lift</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>累积客户占比(%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>累积捕捉率(%)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>累积提升度</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B2" t="n">
+        <v>326</v>
+      </c>
+      <c r="C2" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2" t="n">
+        <v>91.72</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7598974088780676</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.236</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.236</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3" t="n">
+        <v>325</v>
+      </c>
+      <c r="C3" t="n">
+        <v>280</v>
+      </c>
+      <c r="D3" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7221933814025644</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.161</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.198</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>326</v>
+      </c>
+      <c r="C4" t="n">
+        <v>286</v>
+      </c>
+      <c r="D4" t="n">
+        <v>87.73</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.6979124956872498</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.182</v>
+      </c>
+      <c r="G4" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="H4" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.193</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B5" t="n">
+        <v>325</v>
+      </c>
+      <c r="C5" t="n">
+        <v>274</v>
+      </c>
+      <c r="D5" t="n">
+        <v>84.31</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6689361848351983</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.136</v>
+      </c>
+      <c r="G5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" t="n">
+        <v>47.14</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.178</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>325</v>
+      </c>
+      <c r="C6" t="n">
+        <v>262</v>
+      </c>
+      <c r="D6" t="n">
+        <v>80.62</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6132573147878049</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="G6" t="n">
+        <v>49.98</v>
+      </c>
+      <c r="H6" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>326</v>
+      </c>
+      <c r="C7" t="n">
+        <v>256</v>
+      </c>
+      <c r="D7" t="n">
+        <v>78.53</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5565659177632587</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.058</v>
+      </c>
+      <c r="G7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H7" t="n">
+        <v>68.58</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.143</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="n">
+        <v>325</v>
+      </c>
+      <c r="C8" t="n">
+        <v>251</v>
+      </c>
+      <c r="D8" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.48986019867981</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G8" t="n">
+        <v>69.98</v>
+      </c>
+      <c r="H8" t="n">
+        <v>78.97</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.128</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="n">
+        <v>326</v>
+      </c>
+      <c r="C9" t="n">
+        <v>213</v>
+      </c>
+      <c r="D9" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.415359603429984</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G9" t="n">
+        <v>80</v>
+      </c>
+      <c r="H9" t="n">
+        <v>87.79000000000001</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.097</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="n">
+        <v>325</v>
+      </c>
+      <c r="C10" t="n">
+        <v>189</v>
+      </c>
+      <c r="D10" t="n">
+        <v>58.15</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3156203993226715</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="G10" t="n">
+        <v>89.98</v>
+      </c>
+      <c r="H10" t="n">
+        <v>95.61</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.063</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>326</v>
+      </c>
+      <c r="C11" t="n">
+        <v>106</v>
+      </c>
+      <c r="D11" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1588973550465702</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="G11" t="n">
+        <v>100</v>
+      </c>
+      <c r="H11" t="n">
+        <v>100</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27.6" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="11.6" customWidth="1" min="3" max="3"/>
+    <col width="40.40000000000001" customWidth="1" min="4" max="4"/>
+    <col width="11.6" customWidth="1" min="5" max="5"/>
+    <col width="11.6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>客群</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>客户数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>流失率(%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>预测特征</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>CV_AUC</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CV_KS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>一次性客户（历史仅 1 次购买）</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1593</v>
+      </c>
+      <c r="C2" t="n">
+        <v>86.06</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>全量 RFM 行为特征（14 维）</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5481</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.091</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>复购客户（历史 ≥2 次购买）</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1662</v>
+      </c>
+      <c r="C3" t="n">
+        <v>62.88</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>全量 RFM 行为特征（14 维）</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7022</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3148</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>一次性客户（历史仅 1 次购买）</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1593</v>
+      </c>
+      <c r="C4" t="n">
+        <v>86.06</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>首购特征集（6 维：首购金额/品类/距今天数等）</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.5464</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0993</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38.8" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11.6" customWidth="1" min="4" max="4"/>
+    <col width="11.6" customWidth="1" min="5" max="5"/>
+    <col width="11.6" customWidth="1" min="6" max="6"/>
+    <col width="11.6" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>表现窗</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>窗口类型</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>样本客户数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>流失率(%)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>AUC</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PR_AUC</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2011-08-31 ~ 2011-11-30</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>主建模窗口（样本内）</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3255</v>
+      </c>
+      <c r="D2" t="n">
+        <v>74.22</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7292</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8611</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3533</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2011-05-31 ~ 2011-08-31</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>前移 3 个月</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3016</v>
+      </c>
+      <c r="D3" t="n">
+        <v>80.01000000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7439</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3662</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2011-02-28 ~ 2011-05-31</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>前移 6 个月</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2682</v>
+      </c>
+      <c r="D4" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7201</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8895999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3473</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2010-11-30 ~ 2011-02-28</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>前移 9 个月</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2448</v>
+      </c>
+      <c r="D5" t="n">
+        <v>79.48999999999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8777</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3411</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -8538,6 +9922,8460 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I25"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14.8" customWidth="1" min="1" max="1"/>
+    <col width="11.6" customWidth="1" min="2" max="2"/>
+    <col width="13.2" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="13.2" customWidth="1" min="5" max="5"/>
+    <col width="14.8" customWidth="1" min="6" max="6"/>
+    <col width="13.2" customWidth="1" min="7" max="7"/>
+    <col width="14.8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>触达成本率(%)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>挽回率(%)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>触达比例(%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>触达人数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>命中真实流失数</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>挽回金额(£)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>触达成本(£)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>净收益(£)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>163</v>
+      </c>
+      <c r="E2" t="n">
+        <v>146</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5897</v>
+      </c>
+      <c r="G2" t="n">
+        <v>387</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5511</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>50</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>326</v>
+      </c>
+      <c r="E3" t="n">
+        <v>299</v>
+      </c>
+      <c r="F3" t="n">
+        <v>19006</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1215</v>
+      </c>
+      <c r="H3" t="n">
+        <v>17791</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" t="n">
+        <v>651</v>
+      </c>
+      <c r="E4" t="n">
+        <v>579</v>
+      </c>
+      <c r="F4" t="n">
+        <v>55269</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3698</v>
+      </c>
+      <c r="H4" t="n">
+        <v>51571</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D5" t="n">
+        <v>977</v>
+      </c>
+      <c r="E5" t="n">
+        <v>865</v>
+      </c>
+      <c r="F5" t="n">
+        <v>106818</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7161</v>
+      </c>
+      <c r="H5" t="n">
+        <v>99657</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1628</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1402</v>
+      </c>
+      <c r="F6" t="n">
+        <v>235523</v>
+      </c>
+      <c r="G6" t="n">
+        <v>16553</v>
+      </c>
+      <c r="H6" t="n">
+        <v>218970</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>163</v>
+      </c>
+      <c r="E7" t="n">
+        <v>146</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5897</v>
+      </c>
+      <c r="G7" t="n">
+        <v>645</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5253</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>326</v>
+      </c>
+      <c r="E8" t="n">
+        <v>299</v>
+      </c>
+      <c r="F8" t="n">
+        <v>19006</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H8" t="n">
+        <v>16981</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" t="n">
+        <v>651</v>
+      </c>
+      <c r="E9" t="n">
+        <v>579</v>
+      </c>
+      <c r="F9" t="n">
+        <v>55269</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6163</v>
+      </c>
+      <c r="H9" t="n">
+        <v>49106</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>50</v>
+      </c>
+      <c r="C10" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" t="n">
+        <v>977</v>
+      </c>
+      <c r="E10" t="n">
+        <v>865</v>
+      </c>
+      <c r="F10" t="n">
+        <v>106818</v>
+      </c>
+      <c r="G10" t="n">
+        <v>11935</v>
+      </c>
+      <c r="H10" t="n">
+        <v>94883</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1628</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1402</v>
+      </c>
+      <c r="F11" t="n">
+        <v>235523</v>
+      </c>
+      <c r="G11" t="n">
+        <v>27588</v>
+      </c>
+      <c r="H11" t="n">
+        <v>207935</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>30</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>163</v>
+      </c>
+      <c r="E12" t="n">
+        <v>146</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3538</v>
+      </c>
+      <c r="G12" t="n">
+        <v>645</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2894</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" t="n">
+        <v>30</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>326</v>
+      </c>
+      <c r="E13" t="n">
+        <v>299</v>
+      </c>
+      <c r="F13" t="n">
+        <v>11404</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9379</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>30</v>
+      </c>
+      <c r="C14" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" t="n">
+        <v>651</v>
+      </c>
+      <c r="E14" t="n">
+        <v>579</v>
+      </c>
+      <c r="F14" t="n">
+        <v>33161</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6163</v>
+      </c>
+      <c r="H14" t="n">
+        <v>26998</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" t="n">
+        <v>30</v>
+      </c>
+      <c r="C15" t="n">
+        <v>30</v>
+      </c>
+      <c r="D15" t="n">
+        <v>977</v>
+      </c>
+      <c r="E15" t="n">
+        <v>865</v>
+      </c>
+      <c r="F15" t="n">
+        <v>64091</v>
+      </c>
+      <c r="G15" t="n">
+        <v>11935</v>
+      </c>
+      <c r="H15" t="n">
+        <v>52156</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>30</v>
+      </c>
+      <c r="C16" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1628</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1402</v>
+      </c>
+      <c r="F16" t="n">
+        <v>141314</v>
+      </c>
+      <c r="G16" t="n">
+        <v>27588</v>
+      </c>
+      <c r="H16" t="n">
+        <v>113726</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" t="n">
+        <v>30</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>163</v>
+      </c>
+      <c r="E17" t="n">
+        <v>146</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3538</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1290</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" t="n">
+        <v>30</v>
+      </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" t="n">
+        <v>326</v>
+      </c>
+      <c r="E18" t="n">
+        <v>299</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11404</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4050</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7354</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" t="n">
+        <v>30</v>
+      </c>
+      <c r="C19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" t="n">
+        <v>651</v>
+      </c>
+      <c r="E19" t="n">
+        <v>579</v>
+      </c>
+      <c r="F19" t="n">
+        <v>33161</v>
+      </c>
+      <c r="G19" t="n">
+        <v>12326</v>
+      </c>
+      <c r="H19" t="n">
+        <v>20835</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B20" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" t="n">
+        <v>30</v>
+      </c>
+      <c r="D20" t="n">
+        <v>977</v>
+      </c>
+      <c r="E20" t="n">
+        <v>865</v>
+      </c>
+      <c r="F20" t="n">
+        <v>64091</v>
+      </c>
+      <c r="G20" t="n">
+        <v>23871</v>
+      </c>
+      <c r="H20" t="n">
+        <v>40220</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" t="n">
+        <v>30</v>
+      </c>
+      <c r="C21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1628</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1402</v>
+      </c>
+      <c r="F21" t="n">
+        <v>141314</v>
+      </c>
+      <c r="G21" t="n">
+        <v>55175</v>
+      </c>
+      <c r="H21" t="n">
+        <v>86138</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H21"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H301"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="11.6" customWidth="1" min="3" max="3"/>
+    <col width="16.4" customWidth="1" min="4" max="4"/>
+    <col width="16.4" customWidth="1" min="5" max="5"/>
+    <col width="13.2" customWidth="1" min="6" max="6"/>
+    <col width="14.8" customWidth="1" min="7" max="7"/>
+    <col width="13.2" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>CustomerID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PChurn</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>HistValue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Recency</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ExpLoss</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>15749</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5435</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15160.9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>232</v>
+      </c>
+      <c r="G2" t="n">
+        <v>15160.9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8239.950000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>13687</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5753</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11880.84</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>338</v>
+      </c>
+      <c r="G3" t="n">
+        <v>11880.84</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6835.05</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>12415</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="D4" t="n">
+        <v>29624.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7406.08</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4523.63</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>16684</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1267</v>
+      </c>
+      <c r="D5" t="n">
+        <v>28492.9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>105</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2849.29</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3610.05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>12755</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.4352</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8224.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>265</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2741.53</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3579.35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>17450</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="D7" t="n">
+        <v>57209.38</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4767.45</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3398.24</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>18102</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="D8" t="n">
+        <v>122348.43</v>
+      </c>
+      <c r="E8" t="n">
+        <v>35</v>
+      </c>
+      <c r="F8" t="n">
+        <v>42</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3495.67</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3291.17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>16754</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1671</v>
+      </c>
+      <c r="D9" t="n">
+        <v>19009.48</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>427</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1584.12</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3176.48</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>13081</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1642</v>
+      </c>
+      <c r="D10" t="n">
+        <v>18528.13</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>188</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2058.68</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3042.32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>18251</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.4953</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6053.22</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>345</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3026.61</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2998.16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>14646</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150938.41</v>
+      </c>
+      <c r="E12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3773.46</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2747.08</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>15769</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="D13" t="n">
+        <v>39224.88</v>
+      </c>
+      <c r="E13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2614.99</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2667.29</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12454</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6312</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4098.96</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>316</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4098.96</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2587.26</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>12678</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7679.05</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>275</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1535.81</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2359.77</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>15413</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5769</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4011.59</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>591</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2005.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2314.29</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>12753</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6254999999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3590.59</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>262</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3590.59</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2245.91</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>17511</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>25668.69</v>
+      </c>
+      <c r="E18" t="n">
+        <v>13</v>
+      </c>
+      <c r="F18" t="n">
+        <v>57</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1974.51</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2207.51</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>16210</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.2493</v>
+      </c>
+      <c r="D19" t="n">
+        <v>8740</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>209</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1456.67</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2178.88</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>15497</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5114</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4179.78</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>282</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2089.89</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2137.54</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>14028</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6726</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3175.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>450</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3175.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2135.84</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>14733</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.2535</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8278.27</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>170</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1655.65</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2098.54</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>18087</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.1864</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10996.62</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>190</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1221.85</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2049.77</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>13763</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6351</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3196.48</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>335</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3196.48</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2030.08</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>15251</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5779.01</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>398</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1444.75</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2026.12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>12939</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6625.2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>198</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1325.04</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2014.72</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>13902</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7049</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2836.8</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>560</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2836.8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1999.66</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>13340</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.2594</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7679.4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>34</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2559.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1992.04</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>14676</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.6133</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3231.27</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>344</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3231.27</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1981.74</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>14045</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4676.08</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>280</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1169.02</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1977.51</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>14062</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6582.87</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>315</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1316.57</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1966.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>13139</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6229</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3138.04</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>337</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3138.04</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1954.69</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>14156</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="D33" t="n">
+        <v>90725.3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>44</v>
+      </c>
+      <c r="F33" t="n">
+        <v>16</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2061.94</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1950.59</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>12931</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1374</v>
+      </c>
+      <c r="D34" t="n">
+        <v>14114.48</v>
+      </c>
+      <c r="E34" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" t="n">
+        <v>139</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1176.21</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1939.33</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>12378</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5416.32</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>29</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2708.16</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1915.21</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>17107</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="D36" t="n">
+        <v>6247.59</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" t="n">
+        <v>55</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2082.53</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1912.39</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>12557</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.4709</v>
+      </c>
+      <c r="D37" t="n">
+        <v>4010.14</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>156</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1336.71</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1888.37</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>12539</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5119</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3669.22</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>162</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1834.61</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1878.27</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>15523</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.4459</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4158.69</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>302</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1386.23</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1854.36</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>12949</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.4072</v>
+      </c>
+      <c r="D40" t="n">
+        <v>4518.7</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="n">
+        <v>282</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1506.23</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1840.01</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>12758</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.4223</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4256.25</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>176</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1418.75</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1797.41</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>12709</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.1544</v>
+      </c>
+      <c r="D42" t="n">
+        <v>11635.6</v>
+      </c>
+      <c r="E42" t="n">
+        <v>8</v>
+      </c>
+      <c r="F42" t="n">
+        <v>35</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1454.45</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1796.54</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="n">
+        <v>13734</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5184</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3445.34</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>408</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1722.67</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1786.06</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="n">
+        <v>12671</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.6791</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2622.48</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>506</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2622.48</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1780.93</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="n">
+        <v>12380</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.5748</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3094.6</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>428</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1547.3</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1778.78</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>16652</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.2737</v>
+      </c>
+      <c r="D46" t="n">
+        <v>6440.54</v>
+      </c>
+      <c r="E46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>140</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1288.11</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1762.78</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>12754</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.5969</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2949.12</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>135</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2949.12</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1760.33</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>13135</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.5664</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3096</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>96</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3096</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1753.57</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="n">
+        <v>15838</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.0793</v>
+      </c>
+      <c r="D49" t="n">
+        <v>21966.94</v>
+      </c>
+      <c r="E49" t="n">
+        <v>12</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1830.58</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1741.98</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="n">
+        <v>14607</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4434.42</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" t="n">
+        <v>437</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1108.6</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1741.84</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="n">
+        <v>14258</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.2525</v>
+      </c>
+      <c r="D51" t="n">
+        <v>6789.66</v>
+      </c>
+      <c r="E51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>99</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1357.93</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1714.39</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="n">
+        <v>14016</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.2541</v>
+      </c>
+      <c r="D52" t="n">
+        <v>6625.48</v>
+      </c>
+      <c r="E52" t="n">
+        <v>7</v>
+      </c>
+      <c r="F52" t="n">
+        <v>257</v>
+      </c>
+      <c r="G52" t="n">
+        <v>946.5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1683.53</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="n">
+        <v>16131</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="D53" t="n">
+        <v>4360.01</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" t="n">
+        <v>139</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1453.34</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1679.48</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="n">
+        <v>16772</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.4352</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3698.05</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="n">
+        <v>323</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1232.68</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1609.39</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="n">
+        <v>12980</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="D55" t="n">
+        <v>5477.76</v>
+      </c>
+      <c r="E55" t="n">
+        <v>7</v>
+      </c>
+      <c r="F55" t="n">
+        <v>182</v>
+      </c>
+      <c r="G55" t="n">
+        <v>782.54</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="n">
+        <v>15061</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="D56" t="n">
+        <v>42644.35</v>
+      </c>
+      <c r="E56" t="n">
+        <v>39</v>
+      </c>
+      <c r="F56" t="n">
+        <v>71</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1093.44</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1582.11</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="n">
+        <v>13881</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.1698</v>
+      </c>
+      <c r="D57" t="n">
+        <v>9241.18</v>
+      </c>
+      <c r="E57" t="n">
+        <v>8</v>
+      </c>
+      <c r="F57" t="n">
+        <v>113</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1155.15</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1569.15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="n">
+        <v>12744</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4573.71</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4</v>
+      </c>
+      <c r="F58" t="n">
+        <v>148</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1143.43</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="n">
+        <v>13225</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="D59" t="n">
+        <v>5308.02</v>
+      </c>
+      <c r="E59" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" t="n">
+        <v>170</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1061.6</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1530.83</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="n">
+        <v>13802</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.2279</v>
+      </c>
+      <c r="D60" t="n">
+        <v>6666.21</v>
+      </c>
+      <c r="E60" t="n">
+        <v>7</v>
+      </c>
+      <c r="F60" t="n">
+        <v>211</v>
+      </c>
+      <c r="G60" t="n">
+        <v>952.3200000000001</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1519.23</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="n">
+        <v>17829</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.5155</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2936.52</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" t="n">
+        <v>198</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1468.26</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1513.78</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="n">
+        <v>13373</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2868.51</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2</v>
+      </c>
+      <c r="F62" t="n">
+        <v>315</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1434.26</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1500.23</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>12477</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.6352</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2355.95</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>201</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2355.95</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1496.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="n">
+        <v>13093</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.09909999999999999</v>
+      </c>
+      <c r="D64" t="n">
+        <v>15045.48</v>
+      </c>
+      <c r="E64" t="n">
+        <v>16</v>
+      </c>
+      <c r="F64" t="n">
+        <v>175</v>
+      </c>
+      <c r="G64" t="n">
+        <v>940.34</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1491.01</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="n">
+        <v>13209</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3713.92</v>
+      </c>
+      <c r="E65" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" t="n">
+        <v>127</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1237.97</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1448.43</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="n">
+        <v>12653</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3381.73</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" t="n">
+        <v>48</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1690.86</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1447.04</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="n">
+        <v>13941</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.4576</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3161.31</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" t="n">
+        <v>272</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1053.77</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1446.62</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="n">
+        <v>12766</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.4295</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3355.42</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" t="n">
+        <v>234</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1118.47</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1441.15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="n">
+        <v>12432</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.5029</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2862.06</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>72</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2862.06</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1439.33</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="n">
+        <v>12472</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="D70" t="n">
+        <v>4399.2</v>
+      </c>
+      <c r="E70" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" t="n">
+        <v>217</v>
+      </c>
+      <c r="G70" t="n">
+        <v>879.84</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1437.22</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="n">
+        <v>17084</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2253.22</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>296</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2253.22</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1421.78</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="n">
+        <v>12482</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="D72" t="n">
+        <v>4942.65</v>
+      </c>
+      <c r="E72" t="n">
+        <v>7</v>
+      </c>
+      <c r="F72" t="n">
+        <v>476</v>
+      </c>
+      <c r="G72" t="n">
+        <v>706.09</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1417.06</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="n">
+        <v>15808</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.2509</v>
+      </c>
+      <c r="D73" t="n">
+        <v>5627.36</v>
+      </c>
+      <c r="E73" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" t="n">
+        <v>206</v>
+      </c>
+      <c r="G73" t="n">
+        <v>937.89</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1411.9</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="n">
+        <v>13329</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.5184</v>
+      </c>
+      <c r="D74" t="n">
+        <v>2693.62</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" t="n">
+        <v>331</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1346.81</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1396.37</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="n">
+        <v>14049</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.4629</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3012.42</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" t="n">
+        <v>100</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1506.21</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1394.45</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="n">
+        <v>17416</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="D76" t="n">
+        <v>4148.61</v>
+      </c>
+      <c r="E76" t="n">
+        <v>4</v>
+      </c>
+      <c r="F76" t="n">
+        <v>181</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1037.15</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1393.52</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="n">
+        <v>17404</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="D77" t="n">
+        <v>4466.46</v>
+      </c>
+      <c r="E77" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" t="n">
+        <v>56</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1488.82</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1371.2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="n">
+        <v>15093</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="D78" t="n">
+        <v>4872.73</v>
+      </c>
+      <c r="E78" t="n">
+        <v>6</v>
+      </c>
+      <c r="F78" t="n">
+        <v>272</v>
+      </c>
+      <c r="G78" t="n">
+        <v>812.12</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1340.49</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="n">
+        <v>15640</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.1537</v>
+      </c>
+      <c r="D79" t="n">
+        <v>8598.49</v>
+      </c>
+      <c r="E79" t="n">
+        <v>10</v>
+      </c>
+      <c r="F79" t="n">
+        <v>140</v>
+      </c>
+      <c r="G79" t="n">
+        <v>859.85</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1321.59</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="n">
+        <v>15369</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="D80" t="n">
+        <v>4867.02</v>
+      </c>
+      <c r="E80" t="n">
+        <v>7</v>
+      </c>
+      <c r="F80" t="n">
+        <v>415</v>
+      </c>
+      <c r="G80" t="n">
+        <v>695.29</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1319.94</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="n">
+        <v>14063</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.4759</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2769.9</v>
+      </c>
+      <c r="E81" t="n">
+        <v>3</v>
+      </c>
+      <c r="F81" t="n">
+        <v>586</v>
+      </c>
+      <c r="G81" t="n">
+        <v>923.3</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1318.2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="n">
+        <v>12501</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.6506</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2025.39</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>236</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2025.39</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1317.72</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="n">
+        <v>13777</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.0924</v>
+      </c>
+      <c r="D83" t="n">
+        <v>14070</v>
+      </c>
+      <c r="E83" t="n">
+        <v>18</v>
+      </c>
+      <c r="F83" t="n">
+        <v>65</v>
+      </c>
+      <c r="G83" t="n">
+        <v>781.67</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1300.07</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="n">
+        <v>15077</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.5354</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2428.08</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" t="n">
+        <v>394</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1214.04</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1299.99</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="n">
+        <v>16180</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="D85" t="n">
+        <v>11071.72</v>
+      </c>
+      <c r="E85" t="n">
+        <v>8</v>
+      </c>
+      <c r="F85" t="n">
+        <v>27</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1383.96</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1284.32</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="n">
+        <v>17584</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2947.78</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3</v>
+      </c>
+      <c r="F86" t="n">
+        <v>367</v>
+      </c>
+      <c r="G86" t="n">
+        <v>982.59</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1277.27</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="n">
+        <v>17133</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.4711</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2</v>
+      </c>
+      <c r="F87" t="n">
+        <v>90</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1350</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1271.97</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="n">
+        <v>17625</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.5453</v>
+      </c>
+      <c r="D88" t="n">
+        <v>2318.15</v>
+      </c>
+      <c r="E88" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" t="n">
+        <v>346</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1159.08</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1264.09</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="n">
+        <v>12683</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="D89" t="n">
+        <v>3267.9</v>
+      </c>
+      <c r="E89" t="n">
+        <v>4</v>
+      </c>
+      <c r="F89" t="n">
+        <v>226</v>
+      </c>
+      <c r="G89" t="n">
+        <v>816.98</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1252.26</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="n">
+        <v>12429</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="D90" t="n">
+        <v>2305.6</v>
+      </c>
+      <c r="E90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" t="n">
+        <v>265</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1152.8</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1247.33</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="n">
+        <v>13629</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.2842</v>
+      </c>
+      <c r="D91" t="n">
+        <v>4328.5</v>
+      </c>
+      <c r="E91" t="n">
+        <v>5</v>
+      </c>
+      <c r="F91" t="n">
+        <v>36</v>
+      </c>
+      <c r="G91" t="n">
+        <v>865.7</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1230.16</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="n">
+        <v>17381</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.2031</v>
+      </c>
+      <c r="D92" t="n">
+        <v>6017.14</v>
+      </c>
+      <c r="E92" t="n">
+        <v>9</v>
+      </c>
+      <c r="F92" t="n">
+        <v>132</v>
+      </c>
+      <c r="G92" t="n">
+        <v>668.5700000000001</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1222.08</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="n">
+        <v>12714</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3243.36</v>
+      </c>
+      <c r="E93" t="n">
+        <v>4</v>
+      </c>
+      <c r="F93" t="n">
+        <v>194</v>
+      </c>
+      <c r="G93" t="n">
+        <v>810.84</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1221.13</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="n">
+        <v>14680</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="D94" t="n">
+        <v>20633.26</v>
+      </c>
+      <c r="E94" t="n">
+        <v>20</v>
+      </c>
+      <c r="F94" t="n">
+        <v>54</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1031.66</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1213.24</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="n">
+        <v>13027</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2995.2</v>
+      </c>
+      <c r="E95" t="n">
+        <v>3</v>
+      </c>
+      <c r="F95" t="n">
+        <v>57</v>
+      </c>
+      <c r="G95" t="n">
+        <v>998.4</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1210.66</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="n">
+        <v>15050</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2349.5</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" t="n">
+        <v>321</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1174.75</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1207.64</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="n">
+        <v>14298</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.0593</v>
+      </c>
+      <c r="D97" t="n">
+        <v>20310.27</v>
+      </c>
+      <c r="E97" t="n">
+        <v>21</v>
+      </c>
+      <c r="F97" t="n">
+        <v>41</v>
+      </c>
+      <c r="G97" t="n">
+        <v>967.16</v>
+      </c>
+      <c r="H97" t="n">
+        <v>1204.4</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="n">
+        <v>15382</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.2777</v>
+      </c>
+      <c r="D98" t="n">
+        <v>4334.2</v>
+      </c>
+      <c r="E98" t="n">
+        <v>5</v>
+      </c>
+      <c r="F98" t="n">
+        <v>84</v>
+      </c>
+      <c r="G98" t="n">
+        <v>866.84</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1203.61</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="n">
+        <v>14961</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="D99" t="n">
+        <v>7109.8</v>
+      </c>
+      <c r="E99" t="n">
+        <v>10</v>
+      </c>
+      <c r="F99" t="n">
+        <v>197</v>
+      </c>
+      <c r="G99" t="n">
+        <v>710.98</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1198.71</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="n">
+        <v>15786</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="D100" t="n">
+        <v>3147.64</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="n">
+        <v>14</v>
+      </c>
+      <c r="G100" t="n">
+        <v>3147.64</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1187.29</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="n">
+        <v>12917</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.4379</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2696</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3</v>
+      </c>
+      <c r="F101" t="n">
+        <v>300</v>
+      </c>
+      <c r="G101" t="n">
+        <v>898.67</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1180.58</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="n">
+        <v>15032</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.5266</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2236.2</v>
+      </c>
+      <c r="E102" t="n">
+        <v>2</v>
+      </c>
+      <c r="F102" t="n">
+        <v>156</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1118.1</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1177.58</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="n">
+        <v>17949</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D103" t="n">
+        <v>18477.05</v>
+      </c>
+      <c r="E103" t="n">
+        <v>28</v>
+      </c>
+      <c r="F103" t="n">
+        <v>41</v>
+      </c>
+      <c r="G103" t="n">
+        <v>659.89</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1171.44</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="n">
+        <v>17857</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.2286</v>
+      </c>
+      <c r="D104" t="n">
+        <v>5093.88</v>
+      </c>
+      <c r="E104" t="n">
+        <v>3</v>
+      </c>
+      <c r="F104" t="n">
+        <v>9</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1697.96</v>
+      </c>
+      <c r="H104" t="n">
+        <v>1164.46</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="n">
+        <v>16873</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="D105" t="n">
+        <v>3200.22</v>
+      </c>
+      <c r="E105" t="n">
+        <v>3</v>
+      </c>
+      <c r="F105" t="n">
+        <v>97</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1066.74</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1159.76</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="n">
+        <v>15980</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.4015</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2887.82</v>
+      </c>
+      <c r="E106" t="n">
+        <v>3</v>
+      </c>
+      <c r="F106" t="n">
+        <v>154</v>
+      </c>
+      <c r="G106" t="n">
+        <v>962.61</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1159.46</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="n">
+        <v>13458</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.1802</v>
+      </c>
+      <c r="D107" t="n">
+        <v>6409.1</v>
+      </c>
+      <c r="E107" t="n">
+        <v>7</v>
+      </c>
+      <c r="F107" t="n">
+        <v>69</v>
+      </c>
+      <c r="G107" t="n">
+        <v>915.59</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1154.92</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="n">
+        <v>14952</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.2351</v>
+      </c>
+      <c r="D108" t="n">
+        <v>4873.32</v>
+      </c>
+      <c r="E108" t="n">
+        <v>7</v>
+      </c>
+      <c r="F108" t="n">
+        <v>205</v>
+      </c>
+      <c r="G108" t="n">
+        <v>696.1900000000001</v>
+      </c>
+      <c r="H108" t="n">
+        <v>1145.72</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="n">
+        <v>13615</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.4174</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2744.31</v>
+      </c>
+      <c r="E109" t="n">
+        <v>3</v>
+      </c>
+      <c r="F109" t="n">
+        <v>218</v>
+      </c>
+      <c r="G109" t="n">
+        <v>914.77</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1145.47</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="n">
+        <v>12481</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="D110" t="n">
+        <v>3039.16</v>
+      </c>
+      <c r="E110" t="n">
+        <v>4</v>
+      </c>
+      <c r="F110" t="n">
+        <v>236</v>
+      </c>
+      <c r="G110" t="n">
+        <v>759.79</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1126.01</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="n">
+        <v>15934</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.5132</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2190.66</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2</v>
+      </c>
+      <c r="F111" t="n">
+        <v>317</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1095.33</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1124.25</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="n">
+        <v>15476</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.5162</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2173.78</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2</v>
+      </c>
+      <c r="F112" t="n">
+        <v>292</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1086.89</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1122.11</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="n">
+        <v>12385</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.6693</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1668.4</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" t="n">
+        <v>279</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1668.4</v>
+      </c>
+      <c r="H113" t="n">
+        <v>1116.66</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="n">
+        <v>14737</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="D114" t="n">
+        <v>3471.37</v>
+      </c>
+      <c r="E114" t="n">
+        <v>3</v>
+      </c>
+      <c r="F114" t="n">
+        <v>28</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1157.12</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1114.31</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="n">
+        <v>12911</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.6702</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1651.72</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" t="n">
+        <v>451</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1651.72</v>
+      </c>
+      <c r="H115" t="n">
+        <v>1106.98</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="n">
+        <v>16072</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.6504</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1694.64</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" t="n">
+        <v>328</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1694.64</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1102.19</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="n">
+        <v>15768</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="D117" t="n">
+        <v>4202.3</v>
+      </c>
+      <c r="E117" t="n">
+        <v>7</v>
+      </c>
+      <c r="F117" t="n">
+        <v>433</v>
+      </c>
+      <c r="G117" t="n">
+        <v>600.33</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1096.8</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="n">
+        <v>12583</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.1928</v>
+      </c>
+      <c r="D118" t="n">
+        <v>5624.44</v>
+      </c>
+      <c r="E118" t="n">
+        <v>8</v>
+      </c>
+      <c r="F118" t="n">
+        <v>71</v>
+      </c>
+      <c r="G118" t="n">
+        <v>703.0599999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1084.39</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="n">
+        <v>12764</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.6378</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1693.88</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" t="n">
+        <v>216</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1693.88</v>
+      </c>
+      <c r="H119" t="n">
+        <v>1080.36</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="n">
+        <v>12631</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.4922</v>
+      </c>
+      <c r="D120" t="n">
+        <v>2183.25</v>
+      </c>
+      <c r="E120" t="n">
+        <v>3</v>
+      </c>
+      <c r="F120" t="n">
+        <v>444</v>
+      </c>
+      <c r="G120" t="n">
+        <v>727.75</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1074.6</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="n">
+        <v>14292</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.4298</v>
+      </c>
+      <c r="D121" t="n">
+        <v>2488.98</v>
+      </c>
+      <c r="E121" t="n">
+        <v>3</v>
+      </c>
+      <c r="F121" t="n">
+        <v>310</v>
+      </c>
+      <c r="G121" t="n">
+        <v>829.66</v>
+      </c>
+      <c r="H121" t="n">
+        <v>1069.76</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="n">
+        <v>15502</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="D122" t="n">
+        <v>5745.93</v>
+      </c>
+      <c r="E122" t="n">
+        <v>4</v>
+      </c>
+      <c r="F122" t="n">
+        <v>23</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1436.48</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1067.59</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="n">
+        <v>14766</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.5387</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1978.15</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2</v>
+      </c>
+      <c r="F123" t="n">
+        <v>372</v>
+      </c>
+      <c r="G123" t="n">
+        <v>989.08</v>
+      </c>
+      <c r="H123" t="n">
+        <v>1065.63</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="n">
+        <v>12830</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="D124" t="n">
+        <v>2221.84</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" t="n">
+        <v>71</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2221.84</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1064.26</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="n">
+        <v>13297</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1972.77</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2</v>
+      </c>
+      <c r="F125" t="n">
+        <v>322</v>
+      </c>
+      <c r="G125" t="n">
+        <v>986.38</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1061.94</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="n">
+        <v>14544</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.5206</v>
+      </c>
+      <c r="D126" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E126" t="n">
+        <v>2</v>
+      </c>
+      <c r="F126" t="n">
+        <v>261</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1018</v>
+      </c>
+      <c r="H126" t="n">
+        <v>1059.94</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="n">
+        <v>12476</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.2007</v>
+      </c>
+      <c r="D127" t="n">
+        <v>5280.32</v>
+      </c>
+      <c r="E127" t="n">
+        <v>8</v>
+      </c>
+      <c r="F127" t="n">
+        <v>118</v>
+      </c>
+      <c r="G127" t="n">
+        <v>660.04</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1059.76</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="n">
+        <v>17504</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.1991</v>
+      </c>
+      <c r="D128" t="n">
+        <v>5295.38</v>
+      </c>
+      <c r="E128" t="n">
+        <v>7</v>
+      </c>
+      <c r="F128" t="n">
+        <v>106</v>
+      </c>
+      <c r="G128" t="n">
+        <v>756.48</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1054.31</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="n">
+        <v>16253</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.4591</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2279.24</v>
+      </c>
+      <c r="E129" t="n">
+        <v>3</v>
+      </c>
+      <c r="F129" t="n">
+        <v>441</v>
+      </c>
+      <c r="G129" t="n">
+        <v>759.75</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1046.4</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="n">
+        <v>15939</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.2399</v>
+      </c>
+      <c r="D130" t="n">
+        <v>4348.93</v>
+      </c>
+      <c r="E130" t="n">
+        <v>4</v>
+      </c>
+      <c r="F130" t="n">
+        <v>16</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1087.23</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1043.31</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="n">
+        <v>17876</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.6437</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1619.02</v>
+      </c>
+      <c r="E131" t="n">
+        <v>2</v>
+      </c>
+      <c r="F131" t="n">
+        <v>502</v>
+      </c>
+      <c r="G131" t="n">
+        <v>809.51</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1042.16</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="n">
+        <v>17340</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2296.86</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2</v>
+      </c>
+      <c r="F132" t="n">
+        <v>92</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1148.43</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1040.71</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="n">
+        <v>12589</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2218.74</v>
+      </c>
+      <c r="E133" t="n">
+        <v>3</v>
+      </c>
+      <c r="F133" t="n">
+        <v>321</v>
+      </c>
+      <c r="G133" t="n">
+        <v>739.58</v>
+      </c>
+      <c r="H133" t="n">
+        <v>1039.48</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="n">
+        <v>15296</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.2146</v>
+      </c>
+      <c r="D134" t="n">
+        <v>4831.25</v>
+      </c>
+      <c r="E134" t="n">
+        <v>7</v>
+      </c>
+      <c r="F134" t="n">
+        <v>75</v>
+      </c>
+      <c r="G134" t="n">
+        <v>690.1799999999999</v>
+      </c>
+      <c r="H134" t="n">
+        <v>1036.79</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="n">
+        <v>14572</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.4408</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2343.3</v>
+      </c>
+      <c r="E135" t="n">
+        <v>3</v>
+      </c>
+      <c r="F135" t="n">
+        <v>317</v>
+      </c>
+      <c r="G135" t="n">
+        <v>781.1</v>
+      </c>
+      <c r="H135" t="n">
+        <v>1032.93</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="n">
+        <v>17593</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2865.69</v>
+      </c>
+      <c r="E136" t="n">
+        <v>4</v>
+      </c>
+      <c r="F136" t="n">
+        <v>252</v>
+      </c>
+      <c r="G136" t="n">
+        <v>716.42</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1023.34</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="n">
+        <v>15482</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="D137" t="n">
+        <v>2944.45</v>
+      </c>
+      <c r="E137" t="n">
+        <v>4</v>
+      </c>
+      <c r="F137" t="n">
+        <v>150</v>
+      </c>
+      <c r="G137" t="n">
+        <v>736.11</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1021.43</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="n">
+        <v>13334</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.6179</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1637.19</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" t="n">
+        <v>205</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1637.19</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1011.62</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="n">
+        <v>16327</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.4459</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2246.21</v>
+      </c>
+      <c r="E139" t="n">
+        <v>3</v>
+      </c>
+      <c r="F139" t="n">
+        <v>360</v>
+      </c>
+      <c r="G139" t="n">
+        <v>748.74</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1001.59</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="n">
+        <v>14081</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3201.22</v>
+      </c>
+      <c r="E140" t="n">
+        <v>5</v>
+      </c>
+      <c r="F140" t="n">
+        <v>202</v>
+      </c>
+      <c r="G140" t="n">
+        <v>640.24</v>
+      </c>
+      <c r="H140" t="n">
+        <v>995.9</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="n">
+        <v>13178</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.5258</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1870.1</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2</v>
+      </c>
+      <c r="F141" t="n">
+        <v>260</v>
+      </c>
+      <c r="G141" t="n">
+        <v>935.05</v>
+      </c>
+      <c r="H141" t="n">
+        <v>983.3</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="n">
+        <v>16041</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="D142" t="n">
+        <v>2064.8</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" t="n">
+        <v>41</v>
+      </c>
+      <c r="G142" t="n">
+        <v>2064.8</v>
+      </c>
+      <c r="H142" t="n">
+        <v>975.62</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="n">
+        <v>16940</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.4497</v>
+      </c>
+      <c r="D143" t="n">
+        <v>2167.65</v>
+      </c>
+      <c r="E143" t="n">
+        <v>3</v>
+      </c>
+      <c r="F143" t="n">
+        <v>350</v>
+      </c>
+      <c r="G143" t="n">
+        <v>722.55</v>
+      </c>
+      <c r="H143" t="n">
+        <v>974.79</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="n">
+        <v>16795</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.5179</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1869.47</v>
+      </c>
+      <c r="E144" t="n">
+        <v>2</v>
+      </c>
+      <c r="F144" t="n">
+        <v>265</v>
+      </c>
+      <c r="G144" t="n">
+        <v>934.74</v>
+      </c>
+      <c r="H144" t="n">
+        <v>968.2</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="n">
+        <v>15494</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="D145" t="n">
+        <v>3428.66</v>
+      </c>
+      <c r="E145" t="n">
+        <v>3</v>
+      </c>
+      <c r="F145" t="n">
+        <v>21</v>
+      </c>
+      <c r="G145" t="n">
+        <v>1142.89</v>
+      </c>
+      <c r="H145" t="n">
+        <v>967.91</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="n">
+        <v>12540</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="D146" t="n">
+        <v>6451.47</v>
+      </c>
+      <c r="E146" t="n">
+        <v>11</v>
+      </c>
+      <c r="F146" t="n">
+        <v>86</v>
+      </c>
+      <c r="G146" t="n">
+        <v>586.5</v>
+      </c>
+      <c r="H146" t="n">
+        <v>966.4299999999999</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="n">
+        <v>16409</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="D147" t="n">
+        <v>2591.96</v>
+      </c>
+      <c r="E147" t="n">
+        <v>4</v>
+      </c>
+      <c r="F147" t="n">
+        <v>287</v>
+      </c>
+      <c r="G147" t="n">
+        <v>647.99</v>
+      </c>
+      <c r="H147" t="n">
+        <v>966.28</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>12623</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0.4044</v>
+      </c>
+      <c r="D148" t="n">
+        <v>2377.87</v>
+      </c>
+      <c r="E148" t="n">
+        <v>4</v>
+      </c>
+      <c r="F148" t="n">
+        <v>316</v>
+      </c>
+      <c r="G148" t="n">
+        <v>594.47</v>
+      </c>
+      <c r="H148" t="n">
+        <v>961.61</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="n">
+        <v>16320</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0.6912</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1387.5</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>353</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1387.5</v>
+      </c>
+      <c r="H149" t="n">
+        <v>959.04</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="n">
+        <v>13425</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1766.22</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2</v>
+      </c>
+      <c r="F150" t="n">
+        <v>408</v>
+      </c>
+      <c r="G150" t="n">
+        <v>883.11</v>
+      </c>
+      <c r="H150" t="n">
+        <v>957.29</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="n">
+        <v>17139</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.1395</v>
+      </c>
+      <c r="D151" t="n">
+        <v>6843.28</v>
+      </c>
+      <c r="E151" t="n">
+        <v>7</v>
+      </c>
+      <c r="F151" t="n">
+        <v>22</v>
+      </c>
+      <c r="G151" t="n">
+        <v>977.61</v>
+      </c>
+      <c r="H151" t="n">
+        <v>954.64</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="n">
+        <v>17865</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="D152" t="n">
+        <v>3153.16</v>
+      </c>
+      <c r="E152" t="n">
+        <v>5</v>
+      </c>
+      <c r="F152" t="n">
+        <v>195</v>
+      </c>
+      <c r="G152" t="n">
+        <v>630.63</v>
+      </c>
+      <c r="H152" t="n">
+        <v>953.83</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="n">
+        <v>15498</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="D153" t="n">
+        <v>10851.17</v>
+      </c>
+      <c r="E153" t="n">
+        <v>12</v>
+      </c>
+      <c r="F153" t="n">
+        <v>20</v>
+      </c>
+      <c r="G153" t="n">
+        <v>904.26</v>
+      </c>
+      <c r="H153" t="n">
+        <v>953.8200000000001</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="n">
+        <v>14031</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0.07770000000000001</v>
+      </c>
+      <c r="D154" t="n">
+        <v>12275.22</v>
+      </c>
+      <c r="E154" t="n">
+        <v>14</v>
+      </c>
+      <c r="F154" t="n">
+        <v>26</v>
+      </c>
+      <c r="G154" t="n">
+        <v>876.8</v>
+      </c>
+      <c r="H154" t="n">
+        <v>953.78</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="n">
+        <v>17230</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="D155" t="n">
+        <v>2673.81</v>
+      </c>
+      <c r="E155" t="n">
+        <v>4</v>
+      </c>
+      <c r="F155" t="n">
+        <v>210</v>
+      </c>
+      <c r="G155" t="n">
+        <v>668.45</v>
+      </c>
+      <c r="H155" t="n">
+        <v>945.1900000000001</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="n">
+        <v>14145</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0.6805</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1383.6</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" t="n">
+        <v>510</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1383.6</v>
+      </c>
+      <c r="H156" t="n">
+        <v>941.54</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="n">
+        <v>14299</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="D157" t="n">
+        <v>3370.95</v>
+      </c>
+      <c r="E157" t="n">
+        <v>6</v>
+      </c>
+      <c r="F157" t="n">
+        <v>287</v>
+      </c>
+      <c r="G157" t="n">
+        <v>561.8200000000001</v>
+      </c>
+      <c r="H157" t="n">
+        <v>940.5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="n">
+        <v>14566</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0.7089</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1320</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" t="n">
+        <v>317</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1320</v>
+      </c>
+      <c r="H158" t="n">
+        <v>935.75</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="n">
+        <v>16182</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0.4591</v>
+      </c>
+      <c r="D159" t="n">
+        <v>2034</v>
+      </c>
+      <c r="E159" t="n">
+        <v>3</v>
+      </c>
+      <c r="F159" t="n">
+        <v>194</v>
+      </c>
+      <c r="G159" t="n">
+        <v>678</v>
+      </c>
+      <c r="H159" t="n">
+        <v>933.8099999999999</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>15125</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="D160" t="n">
+        <v>7616.06</v>
+      </c>
+      <c r="E160" t="n">
+        <v>8</v>
+      </c>
+      <c r="F160" t="n">
+        <v>13</v>
+      </c>
+      <c r="G160" t="n">
+        <v>952.01</v>
+      </c>
+      <c r="H160" t="n">
+        <v>932.97</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>12681</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="D161" t="n">
+        <v>7495.67</v>
+      </c>
+      <c r="E161" t="n">
+        <v>12</v>
+      </c>
+      <c r="F161" t="n">
+        <v>51</v>
+      </c>
+      <c r="G161" t="n">
+        <v>624.64</v>
+      </c>
+      <c r="H161" t="n">
+        <v>930.21</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>17044</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.6444</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1441</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" t="n">
+        <v>274</v>
+      </c>
+      <c r="G162" t="n">
+        <v>1441</v>
+      </c>
+      <c r="H162" t="n">
+        <v>928.58</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="n">
+        <v>13564</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0.1671</v>
+      </c>
+      <c r="D163" t="n">
+        <v>5519.63</v>
+      </c>
+      <c r="E163" t="n">
+        <v>11</v>
+      </c>
+      <c r="F163" t="n">
+        <v>254</v>
+      </c>
+      <c r="G163" t="n">
+        <v>501.78</v>
+      </c>
+      <c r="H163" t="n">
+        <v>922.33</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="n">
+        <v>14936</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0.2489</v>
+      </c>
+      <c r="D164" t="n">
+        <v>3703.88</v>
+      </c>
+      <c r="E164" t="n">
+        <v>3</v>
+      </c>
+      <c r="F164" t="n">
+        <v>8</v>
+      </c>
+      <c r="G164" t="n">
+        <v>1234.63</v>
+      </c>
+      <c r="H164" t="n">
+        <v>921.9</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="n">
+        <v>15034</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="D165" t="n">
+        <v>3131.57</v>
+      </c>
+      <c r="E165" t="n">
+        <v>5</v>
+      </c>
+      <c r="F165" t="n">
+        <v>178</v>
+      </c>
+      <c r="G165" t="n">
+        <v>626.3099999999999</v>
+      </c>
+      <c r="H165" t="n">
+        <v>921.62</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="n">
+        <v>16191</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="D166" t="n">
+        <v>2982.04</v>
+      </c>
+      <c r="E166" t="n">
+        <v>6</v>
+      </c>
+      <c r="F166" t="n">
+        <v>201</v>
+      </c>
+      <c r="G166" t="n">
+        <v>497.01</v>
+      </c>
+      <c r="H166" t="n">
+        <v>916.6799999999999</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="n">
+        <v>14154</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0.6556999999999999</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1396.34</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" t="n">
+        <v>323</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1396.34</v>
+      </c>
+      <c r="H167" t="n">
+        <v>915.58</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="n">
+        <v>16333</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="D168" t="n">
+        <v>2535.52</v>
+      </c>
+      <c r="E168" t="n">
+        <v>4</v>
+      </c>
+      <c r="F168" t="n">
+        <v>140</v>
+      </c>
+      <c r="G168" t="n">
+        <v>633.88</v>
+      </c>
+      <c r="H168" t="n">
+        <v>912.28</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="n">
+        <v>13162</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="D169" t="n">
+        <v>3245.99</v>
+      </c>
+      <c r="E169" t="n">
+        <v>6</v>
+      </c>
+      <c r="F169" t="n">
+        <v>280</v>
+      </c>
+      <c r="G169" t="n">
+        <v>541</v>
+      </c>
+      <c r="H169" t="n">
+        <v>911.8</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="n">
+        <v>12643</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0.4298</v>
+      </c>
+      <c r="D170" t="n">
+        <v>2113.68</v>
+      </c>
+      <c r="E170" t="n">
+        <v>3</v>
+      </c>
+      <c r="F170" t="n">
+        <v>82</v>
+      </c>
+      <c r="G170" t="n">
+        <v>704.5599999999999</v>
+      </c>
+      <c r="H170" t="n">
+        <v>908.46</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="n">
+        <v>15513</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="D171" t="n">
+        <v>5564.17</v>
+      </c>
+      <c r="E171" t="n">
+        <v>10</v>
+      </c>
+      <c r="F171" t="n">
+        <v>160</v>
+      </c>
+      <c r="G171" t="n">
+        <v>556.42</v>
+      </c>
+      <c r="H171" t="n">
+        <v>905.29</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="n">
+        <v>18026</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0.6807</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1328.65</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" t="n">
+        <v>400</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1328.65</v>
+      </c>
+      <c r="H172" t="n">
+        <v>904.41</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="n">
+        <v>13316</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.2568</v>
+      </c>
+      <c r="D173" t="n">
+        <v>3520.5</v>
+      </c>
+      <c r="E173" t="n">
+        <v>3</v>
+      </c>
+      <c r="F173" t="n">
+        <v>31</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1173.5</v>
+      </c>
+      <c r="H173" t="n">
+        <v>904.0599999999999</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="n">
+        <v>17716</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.2183</v>
+      </c>
+      <c r="D174" t="n">
+        <v>4126.86</v>
+      </c>
+      <c r="E174" t="n">
+        <v>7</v>
+      </c>
+      <c r="F174" t="n">
+        <v>149</v>
+      </c>
+      <c r="G174" t="n">
+        <v>589.55</v>
+      </c>
+      <c r="H174" t="n">
+        <v>900.89</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="n">
+        <v>16153</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1674.23</v>
+      </c>
+      <c r="E175" t="n">
+        <v>2</v>
+      </c>
+      <c r="F175" t="n">
+        <v>421</v>
+      </c>
+      <c r="G175" t="n">
+        <v>837.12</v>
+      </c>
+      <c r="H175" t="n">
+        <v>899.9</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="n">
+        <v>14875</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.6429</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1397.08</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" t="n">
+        <v>341</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1397.08</v>
+      </c>
+      <c r="H176" t="n">
+        <v>898.1799999999999</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="n">
+        <v>13680</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0.5292</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1695.29</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2</v>
+      </c>
+      <c r="F177" t="n">
+        <v>239</v>
+      </c>
+      <c r="G177" t="n">
+        <v>847.64</v>
+      </c>
+      <c r="H177" t="n">
+        <v>897.15</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="n">
+        <v>13015</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="D178" t="n">
+        <v>2906.4</v>
+      </c>
+      <c r="E178" t="n">
+        <v>4</v>
+      </c>
+      <c r="F178" t="n">
+        <v>97</v>
+      </c>
+      <c r="G178" t="n">
+        <v>726.6</v>
+      </c>
+      <c r="H178" t="n">
+        <v>894.01</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="n">
+        <v>13384</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="D179" t="n">
+        <v>2118.78</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2</v>
+      </c>
+      <c r="F179" t="n">
+        <v>78</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1059.39</v>
+      </c>
+      <c r="H179" t="n">
+        <v>888.1900000000001</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="n">
+        <v>18079</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="D180" t="n">
+        <v>2206.18</v>
+      </c>
+      <c r="E180" t="n">
+        <v>2</v>
+      </c>
+      <c r="F180" t="n">
+        <v>26</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1103.09</v>
+      </c>
+      <c r="H180" t="n">
+        <v>887.55</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="n">
+        <v>12637</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="D181" t="n">
+        <v>2533.05</v>
+      </c>
+      <c r="E181" t="n">
+        <v>4</v>
+      </c>
+      <c r="F181" t="n">
+        <v>139</v>
+      </c>
+      <c r="G181" t="n">
+        <v>633.26</v>
+      </c>
+      <c r="H181" t="n">
+        <v>887.0700000000001</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="n">
+        <v>13455</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1385.88</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>266</v>
+      </c>
+      <c r="G182" t="n">
+        <v>1385.88</v>
+      </c>
+      <c r="H182" t="n">
+        <v>886.96</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="n">
+        <v>15629</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0.5367</v>
+      </c>
+      <c r="D183" t="n">
+        <v>1646.98</v>
+      </c>
+      <c r="E183" t="n">
+        <v>2</v>
+      </c>
+      <c r="F183" t="n">
+        <v>397</v>
+      </c>
+      <c r="G183" t="n">
+        <v>823.49</v>
+      </c>
+      <c r="H183" t="n">
+        <v>883.9299999999999</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="n">
+        <v>17061</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="D184" t="n">
+        <v>2422.87</v>
+      </c>
+      <c r="E184" t="n">
+        <v>3</v>
+      </c>
+      <c r="F184" t="n">
+        <v>118</v>
+      </c>
+      <c r="G184" t="n">
+        <v>807.62</v>
+      </c>
+      <c r="H184" t="n">
+        <v>882.89</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="n">
+        <v>16858</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.5628</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1560.02</v>
+      </c>
+      <c r="E185" t="n">
+        <v>2</v>
+      </c>
+      <c r="F185" t="n">
+        <v>355</v>
+      </c>
+      <c r="G185" t="n">
+        <v>780.01</v>
+      </c>
+      <c r="H185" t="n">
+        <v>877.98</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="n">
+        <v>14426</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="D186" t="n">
+        <v>4416.69</v>
+      </c>
+      <c r="E186" t="n">
+        <v>6</v>
+      </c>
+      <c r="F186" t="n">
+        <v>40</v>
+      </c>
+      <c r="G186" t="n">
+        <v>736.11</v>
+      </c>
+      <c r="H186" t="n">
+        <v>870.53</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="n">
+        <v>15673</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="D187" t="n">
+        <v>3007.88</v>
+      </c>
+      <c r="E187" t="n">
+        <v>4</v>
+      </c>
+      <c r="F187" t="n">
+        <v>56</v>
+      </c>
+      <c r="G187" t="n">
+        <v>751.97</v>
+      </c>
+      <c r="H187" t="n">
+        <v>869.88</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="n">
+        <v>16029</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="D188" t="n">
+        <v>24083.16</v>
+      </c>
+      <c r="E188" t="n">
+        <v>29</v>
+      </c>
+      <c r="F188" t="n">
+        <v>7</v>
+      </c>
+      <c r="G188" t="n">
+        <v>830.45</v>
+      </c>
+      <c r="H188" t="n">
+        <v>869.4</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="n">
+        <v>12524</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="D189" t="n">
+        <v>3068.08</v>
+      </c>
+      <c r="E189" t="n">
+        <v>5</v>
+      </c>
+      <c r="F189" t="n">
+        <v>62</v>
+      </c>
+      <c r="G189" t="n">
+        <v>613.62</v>
+      </c>
+      <c r="H189" t="n">
+        <v>866.4299999999999</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="n">
+        <v>14899</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.6476</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1331.38</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1</v>
+      </c>
+      <c r="F190" t="n">
+        <v>295</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1331.38</v>
+      </c>
+      <c r="H190" t="n">
+        <v>862.2</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="n">
+        <v>18194</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.5899</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1456.5</v>
+      </c>
+      <c r="E191" t="n">
+        <v>2</v>
+      </c>
+      <c r="F191" t="n">
+        <v>338</v>
+      </c>
+      <c r="G191" t="n">
+        <v>728.25</v>
+      </c>
+      <c r="H191" t="n">
+        <v>859.1900000000001</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="n">
+        <v>15797</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="D192" t="n">
+        <v>1825.2</v>
+      </c>
+      <c r="E192" t="n">
+        <v>2</v>
+      </c>
+      <c r="F192" t="n">
+        <v>114</v>
+      </c>
+      <c r="G192" t="n">
+        <v>912.6</v>
+      </c>
+      <c r="H192" t="n">
+        <v>859.12</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="n">
+        <v>12437</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2545.63</v>
+      </c>
+      <c r="E193" t="n">
+        <v>5</v>
+      </c>
+      <c r="F193" t="n">
+        <v>189</v>
+      </c>
+      <c r="G193" t="n">
+        <v>509.13</v>
+      </c>
+      <c r="H193" t="n">
+        <v>854.0599999999999</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="n">
+        <v>14101</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="D194" t="n">
+        <v>3176.04</v>
+      </c>
+      <c r="E194" t="n">
+        <v>4</v>
+      </c>
+      <c r="F194" t="n">
+        <v>42</v>
+      </c>
+      <c r="G194" t="n">
+        <v>794.01</v>
+      </c>
+      <c r="H194" t="n">
+        <v>854.04</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="n">
+        <v>16705</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.2015</v>
+      </c>
+      <c r="D195" t="n">
+        <v>4226.48</v>
+      </c>
+      <c r="E195" t="n">
+        <v>8</v>
+      </c>
+      <c r="F195" t="n">
+        <v>141</v>
+      </c>
+      <c r="G195" t="n">
+        <v>528.3099999999999</v>
+      </c>
+      <c r="H195" t="n">
+        <v>851.64</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="n">
+        <v>14249</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1870.09</v>
+      </c>
+      <c r="E196" t="n">
+        <v>3</v>
+      </c>
+      <c r="F196" t="n">
+        <v>451</v>
+      </c>
+      <c r="G196" t="n">
+        <v>623.36</v>
+      </c>
+      <c r="H196" t="n">
+        <v>849.02</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="n">
+        <v>16636</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0.6546999999999999</v>
+      </c>
+      <c r="D197" t="n">
+        <v>1295.25</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" t="n">
+        <v>338</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1295.25</v>
+      </c>
+      <c r="H197" t="n">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="n">
+        <v>12798</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0.5262</v>
+      </c>
+      <c r="D198" t="n">
+        <v>1607.04</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" t="n">
+        <v>70</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1607.04</v>
+      </c>
+      <c r="H198" t="n">
+        <v>845.62</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="n">
+        <v>13448</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="D199" t="n">
+        <v>3020.65</v>
+      </c>
+      <c r="E199" t="n">
+        <v>5</v>
+      </c>
+      <c r="F199" t="n">
+        <v>118</v>
+      </c>
+      <c r="G199" t="n">
+        <v>604.13</v>
+      </c>
+      <c r="H199" t="n">
+        <v>843.67</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="n">
+        <v>13381</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="D200" t="n">
+        <v>2238.57</v>
+      </c>
+      <c r="E200" t="n">
+        <v>3</v>
+      </c>
+      <c r="F200" t="n">
+        <v>107</v>
+      </c>
+      <c r="G200" t="n">
+        <v>746.1900000000001</v>
+      </c>
+      <c r="H200" t="n">
+        <v>843.49</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="n">
+        <v>14911</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="D201" t="n">
+        <v>65203.68</v>
+      </c>
+      <c r="E201" t="n">
+        <v>70</v>
+      </c>
+      <c r="F201" t="n">
+        <v>13</v>
+      </c>
+      <c r="G201" t="n">
+        <v>931.48</v>
+      </c>
+      <c r="H201" t="n">
+        <v>841.13</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="n">
+        <v>16004</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1768.19</v>
+      </c>
+      <c r="E202" t="n">
+        <v>3</v>
+      </c>
+      <c r="F202" t="n">
+        <v>374</v>
+      </c>
+      <c r="G202" t="n">
+        <v>589.4</v>
+      </c>
+      <c r="H202" t="n">
+        <v>838.65</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="n">
+        <v>13478</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0.6807</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1225.2</v>
+      </c>
+      <c r="E203" t="n">
+        <v>1</v>
+      </c>
+      <c r="F203" t="n">
+        <v>532</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1225.2</v>
+      </c>
+      <c r="H203" t="n">
+        <v>833.99</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="n">
+        <v>13694</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="D204" t="n">
+        <v>37553.54</v>
+      </c>
+      <c r="E204" t="n">
+        <v>34</v>
+      </c>
+      <c r="F204" t="n">
+        <v>7</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1104.52</v>
+      </c>
+      <c r="H204" t="n">
+        <v>833.6900000000001</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="n">
+        <v>16013</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="D205" t="n">
+        <v>12466.32</v>
+      </c>
+      <c r="E205" t="n">
+        <v>19</v>
+      </c>
+      <c r="F205" t="n">
+        <v>9</v>
+      </c>
+      <c r="G205" t="n">
+        <v>656.12</v>
+      </c>
+      <c r="H205" t="n">
+        <v>831.5</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="n">
+        <v>13327</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="D206" t="n">
+        <v>2310.06</v>
+      </c>
+      <c r="E206" t="n">
+        <v>4</v>
+      </c>
+      <c r="F206" t="n">
+        <v>195</v>
+      </c>
+      <c r="G206" t="n">
+        <v>577.52</v>
+      </c>
+      <c r="H206" t="n">
+        <v>829.3099999999999</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="n">
+        <v>18092</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0.1701</v>
+      </c>
+      <c r="D207" t="n">
+        <v>4864.56</v>
+      </c>
+      <c r="E207" t="n">
+        <v>7</v>
+      </c>
+      <c r="F207" t="n">
+        <v>19</v>
+      </c>
+      <c r="G207" t="n">
+        <v>694.9400000000001</v>
+      </c>
+      <c r="H207" t="n">
+        <v>827.46</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="n">
+        <v>16008</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0.4269</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1926.99</v>
+      </c>
+      <c r="E208" t="n">
+        <v>3</v>
+      </c>
+      <c r="F208" t="n">
+        <v>282</v>
+      </c>
+      <c r="G208" t="n">
+        <v>642.33</v>
+      </c>
+      <c r="H208" t="n">
+        <v>822.63</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="n">
+        <v>17621</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.6394</v>
+      </c>
+      <c r="D209" t="n">
+        <v>1281.82</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1</v>
+      </c>
+      <c r="F209" t="n">
+        <v>331</v>
+      </c>
+      <c r="G209" t="n">
+        <v>1281.82</v>
+      </c>
+      <c r="H209" t="n">
+        <v>819.6</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="n">
+        <v>15171</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0.6354</v>
+      </c>
+      <c r="D210" t="n">
+        <v>1289.5</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1</v>
+      </c>
+      <c r="F210" t="n">
+        <v>231</v>
+      </c>
+      <c r="G210" t="n">
+        <v>1289.5</v>
+      </c>
+      <c r="H210" t="n">
+        <v>819.35</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="n">
+        <v>15981</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="D211" t="n">
+        <v>2430.14</v>
+      </c>
+      <c r="E211" t="n">
+        <v>4</v>
+      </c>
+      <c r="F211" t="n">
+        <v>141</v>
+      </c>
+      <c r="G211" t="n">
+        <v>607.54</v>
+      </c>
+      <c r="H211" t="n">
+        <v>817.99</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="n">
+        <v>14828</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1782.28</v>
+      </c>
+      <c r="E212" t="n">
+        <v>2</v>
+      </c>
+      <c r="F212" t="n">
+        <v>96</v>
+      </c>
+      <c r="G212" t="n">
+        <v>891.14</v>
+      </c>
+      <c r="H212" t="n">
+        <v>817.53</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="n">
+        <v>17819</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0.3979</v>
+      </c>
+      <c r="D213" t="n">
+        <v>2054.51</v>
+      </c>
+      <c r="E213" t="n">
+        <v>3</v>
+      </c>
+      <c r="F213" t="n">
+        <v>82</v>
+      </c>
+      <c r="G213" t="n">
+        <v>684.84</v>
+      </c>
+      <c r="H213" t="n">
+        <v>817.49</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>12989</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0.1248</v>
+      </c>
+      <c r="D214" t="n">
+        <v>6545.24</v>
+      </c>
+      <c r="E214" t="n">
+        <v>13</v>
+      </c>
+      <c r="F214" t="n">
+        <v>57</v>
+      </c>
+      <c r="G214" t="n">
+        <v>503.48</v>
+      </c>
+      <c r="H214" t="n">
+        <v>816.85</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>15270</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="D215" t="n">
+        <v>2054.42</v>
+      </c>
+      <c r="E215" t="n">
+        <v>4</v>
+      </c>
+      <c r="F215" t="n">
+        <v>300</v>
+      </c>
+      <c r="G215" t="n">
+        <v>513.6</v>
+      </c>
+      <c r="H215" t="n">
+        <v>816.4299999999999</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="n">
+        <v>13798</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0.0346</v>
+      </c>
+      <c r="D216" t="n">
+        <v>23562.8</v>
+      </c>
+      <c r="E216" t="n">
+        <v>31</v>
+      </c>
+      <c r="F216" t="n">
+        <v>23</v>
+      </c>
+      <c r="G216" t="n">
+        <v>760.09</v>
+      </c>
+      <c r="H216" t="n">
+        <v>815.27</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>16993</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D217" t="n">
+        <v>1231.15</v>
+      </c>
+      <c r="E217" t="n">
+        <v>1</v>
+      </c>
+      <c r="F217" t="n">
+        <v>363</v>
+      </c>
+      <c r="G217" t="n">
+        <v>1231.15</v>
+      </c>
+      <c r="H217" t="n">
+        <v>812.5599999999999</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>15321</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="D218" t="n">
+        <v>2663.71</v>
+      </c>
+      <c r="E218" t="n">
+        <v>6</v>
+      </c>
+      <c r="F218" t="n">
+        <v>463</v>
+      </c>
+      <c r="G218" t="n">
+        <v>443.95</v>
+      </c>
+      <c r="H218" t="n">
+        <v>810.3</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="n">
+        <v>12733</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="D219" t="n">
+        <v>1130.22</v>
+      </c>
+      <c r="E219" t="n">
+        <v>1</v>
+      </c>
+      <c r="F219" t="n">
+        <v>589</v>
+      </c>
+      <c r="G219" t="n">
+        <v>1130.22</v>
+      </c>
+      <c r="H219" t="n">
+        <v>806.98</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>12749</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="D220" t="n">
+        <v>2037.75</v>
+      </c>
+      <c r="E220" t="n">
+        <v>3</v>
+      </c>
+      <c r="F220" t="n">
+        <v>113</v>
+      </c>
+      <c r="G220" t="n">
+        <v>679.25</v>
+      </c>
+      <c r="H220" t="n">
+        <v>804.91</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="n">
+        <v>12567</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0.5583</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1441.58</v>
+      </c>
+      <c r="E221" t="n">
+        <v>2</v>
+      </c>
+      <c r="F221" t="n">
+        <v>208</v>
+      </c>
+      <c r="G221" t="n">
+        <v>720.79</v>
+      </c>
+      <c r="H221" t="n">
+        <v>804.83</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="n">
+        <v>17508</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1999.99</v>
+      </c>
+      <c r="E222" t="n">
+        <v>4</v>
+      </c>
+      <c r="F222" t="n">
+        <v>281</v>
+      </c>
+      <c r="G222" t="n">
+        <v>500</v>
+      </c>
+      <c r="H222" t="n">
+        <v>803.8</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="n">
+        <v>13328</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0.6141</v>
+      </c>
+      <c r="D223" t="n">
+        <v>1308.48</v>
+      </c>
+      <c r="E223" t="n">
+        <v>1</v>
+      </c>
+      <c r="F223" t="n">
+        <v>216</v>
+      </c>
+      <c r="G223" t="n">
+        <v>1308.48</v>
+      </c>
+      <c r="H223" t="n">
+        <v>803.54</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="n">
+        <v>13520</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.4987</v>
+      </c>
+      <c r="D224" t="n">
+        <v>1609.3</v>
+      </c>
+      <c r="E224" t="n">
+        <v>3</v>
+      </c>
+      <c r="F224" t="n">
+        <v>376</v>
+      </c>
+      <c r="G224" t="n">
+        <v>536.4299999999999</v>
+      </c>
+      <c r="H224" t="n">
+        <v>802.5599999999999</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="n">
+        <v>14918</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.2678</v>
+      </c>
+      <c r="D225" t="n">
+        <v>2983.29</v>
+      </c>
+      <c r="E225" t="n">
+        <v>4</v>
+      </c>
+      <c r="F225" t="n">
+        <v>54</v>
+      </c>
+      <c r="G225" t="n">
+        <v>745.8200000000001</v>
+      </c>
+      <c r="H225" t="n">
+        <v>798.9299999999999</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="n">
+        <v>12656</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="D226" t="n">
+        <v>2849.88</v>
+      </c>
+      <c r="E226" t="n">
+        <v>3</v>
+      </c>
+      <c r="F226" t="n">
+        <v>16</v>
+      </c>
+      <c r="G226" t="n">
+        <v>949.96</v>
+      </c>
+      <c r="H226" t="n">
+        <v>798.8200000000001</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="n">
+        <v>13097</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0.2156</v>
+      </c>
+      <c r="D227" t="n">
+        <v>3702.3</v>
+      </c>
+      <c r="E227" t="n">
+        <v>8</v>
+      </c>
+      <c r="F227" t="n">
+        <v>192</v>
+      </c>
+      <c r="G227" t="n">
+        <v>462.79</v>
+      </c>
+      <c r="H227" t="n">
+        <v>798.22</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="n">
+        <v>14001</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="D228" t="n">
+        <v>2046.98</v>
+      </c>
+      <c r="E228" t="n">
+        <v>3</v>
+      </c>
+      <c r="F228" t="n">
+        <v>132</v>
+      </c>
+      <c r="G228" t="n">
+        <v>682.33</v>
+      </c>
+      <c r="H228" t="n">
+        <v>797.3</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="n">
+        <v>12428</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="D229" t="n">
+        <v>2586.94</v>
+      </c>
+      <c r="E229" t="n">
+        <v>3</v>
+      </c>
+      <c r="F229" t="n">
+        <v>20</v>
+      </c>
+      <c r="G229" t="n">
+        <v>862.3099999999999</v>
+      </c>
+      <c r="H229" t="n">
+        <v>797.04</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="n">
+        <v>17977</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0.6496</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1223.31</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1</v>
+      </c>
+      <c r="F230" t="n">
+        <v>300</v>
+      </c>
+      <c r="G230" t="n">
+        <v>1223.31</v>
+      </c>
+      <c r="H230" t="n">
+        <v>794.66</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="n">
+        <v>12779</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="D231" t="n">
+        <v>1945.45</v>
+      </c>
+      <c r="E231" t="n">
+        <v>4</v>
+      </c>
+      <c r="F231" t="n">
+        <v>271</v>
+      </c>
+      <c r="G231" t="n">
+        <v>486.36</v>
+      </c>
+      <c r="H231" t="n">
+        <v>791.8</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="n">
+        <v>13361</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1450.5</v>
+      </c>
+      <c r="E232" t="n">
+        <v>2</v>
+      </c>
+      <c r="F232" t="n">
+        <v>372</v>
+      </c>
+      <c r="G232" t="n">
+        <v>725.25</v>
+      </c>
+      <c r="H232" t="n">
+        <v>791.54</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="n">
+        <v>12867</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="D233" t="n">
+        <v>2428.33</v>
+      </c>
+      <c r="E233" t="n">
+        <v>4</v>
+      </c>
+      <c r="F233" t="n">
+        <v>114</v>
+      </c>
+      <c r="G233" t="n">
+        <v>607.08</v>
+      </c>
+      <c r="H233" t="n">
+        <v>787.75</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="n">
+        <v>12901</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.1694</v>
+      </c>
+      <c r="D234" t="n">
+        <v>4642.33</v>
+      </c>
+      <c r="E234" t="n">
+        <v>7</v>
+      </c>
+      <c r="F234" t="n">
+        <v>33</v>
+      </c>
+      <c r="G234" t="n">
+        <v>663.1900000000001</v>
+      </c>
+      <c r="H234" t="n">
+        <v>786.41</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="n">
+        <v>17567</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0.5002</v>
+      </c>
+      <c r="D235" t="n">
+        <v>1571.28</v>
+      </c>
+      <c r="E235" t="n">
+        <v>2</v>
+      </c>
+      <c r="F235" t="n">
+        <v>181</v>
+      </c>
+      <c r="G235" t="n">
+        <v>785.64</v>
+      </c>
+      <c r="H235" t="n">
+        <v>785.95</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="n">
+        <v>16716</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0.5552</v>
+      </c>
+      <c r="D236" t="n">
+        <v>1415.28</v>
+      </c>
+      <c r="E236" t="n">
+        <v>2</v>
+      </c>
+      <c r="F236" t="n">
+        <v>166</v>
+      </c>
+      <c r="G236" t="n">
+        <v>707.64</v>
+      </c>
+      <c r="H236" t="n">
+        <v>785.76</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="n">
+        <v>16316</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="D237" t="n">
+        <v>2844.14</v>
+      </c>
+      <c r="E237" t="n">
+        <v>5</v>
+      </c>
+      <c r="F237" t="n">
+        <v>106</v>
+      </c>
+      <c r="G237" t="n">
+        <v>568.83</v>
+      </c>
+      <c r="H237" t="n">
+        <v>781.5700000000001</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="n">
+        <v>13001</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0.1535</v>
+      </c>
+      <c r="D238" t="n">
+        <v>5069.42</v>
+      </c>
+      <c r="E238" t="n">
+        <v>9</v>
+      </c>
+      <c r="F238" t="n">
+        <v>84</v>
+      </c>
+      <c r="G238" t="n">
+        <v>563.27</v>
+      </c>
+      <c r="H238" t="n">
+        <v>778.16</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="n">
+        <v>13707</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.4212</v>
+      </c>
+      <c r="D239" t="n">
+        <v>1843.01</v>
+      </c>
+      <c r="E239" t="n">
+        <v>3</v>
+      </c>
+      <c r="F239" t="n">
+        <v>215</v>
+      </c>
+      <c r="G239" t="n">
+        <v>614.34</v>
+      </c>
+      <c r="H239" t="n">
+        <v>776.28</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="n">
+        <v>16336</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="D240" t="n">
+        <v>1166.99</v>
+      </c>
+      <c r="E240" t="n">
+        <v>1</v>
+      </c>
+      <c r="F240" t="n">
+        <v>358</v>
+      </c>
+      <c r="G240" t="n">
+        <v>1166.99</v>
+      </c>
+      <c r="H240" t="n">
+        <v>775.11</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="n">
+        <v>13979</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.5492</v>
+      </c>
+      <c r="D241" t="n">
+        <v>1410.53</v>
+      </c>
+      <c r="E241" t="n">
+        <v>2</v>
+      </c>
+      <c r="F241" t="n">
+        <v>293</v>
+      </c>
+      <c r="G241" t="n">
+        <v>705.26</v>
+      </c>
+      <c r="H241" t="n">
+        <v>774.66</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="n">
+        <v>17428</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.1277</v>
+      </c>
+      <c r="D242" t="n">
+        <v>6064.58</v>
+      </c>
+      <c r="E242" t="n">
+        <v>8</v>
+      </c>
+      <c r="F242" t="n">
+        <v>27</v>
+      </c>
+      <c r="G242" t="n">
+        <v>758.0700000000001</v>
+      </c>
+      <c r="H242" t="n">
+        <v>774.45</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="n">
+        <v>13157</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="D243" t="n">
+        <v>2768.86</v>
+      </c>
+      <c r="E243" t="n">
+        <v>4</v>
+      </c>
+      <c r="F243" t="n">
+        <v>41</v>
+      </c>
+      <c r="G243" t="n">
+        <v>692.22</v>
+      </c>
+      <c r="H243" t="n">
+        <v>772.51</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="n">
+        <v>14461</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0.2636</v>
+      </c>
+      <c r="D244" t="n">
+        <v>2928.12</v>
+      </c>
+      <c r="E244" t="n">
+        <v>6</v>
+      </c>
+      <c r="F244" t="n">
+        <v>161</v>
+      </c>
+      <c r="G244" t="n">
+        <v>488.02</v>
+      </c>
+      <c r="H244" t="n">
+        <v>771.85</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="n">
+        <v>18145</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="D245" t="n">
+        <v>1755.25</v>
+      </c>
+      <c r="E245" t="n">
+        <v>3</v>
+      </c>
+      <c r="F245" t="n">
+        <v>212</v>
+      </c>
+      <c r="G245" t="n">
+        <v>585.08</v>
+      </c>
+      <c r="H245" t="n">
+        <v>770.91</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="n">
+        <v>17306</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="D246" t="n">
+        <v>2411.78</v>
+      </c>
+      <c r="E246" t="n">
+        <v>4</v>
+      </c>
+      <c r="F246" t="n">
+        <v>75</v>
+      </c>
+      <c r="G246" t="n">
+        <v>602.9400000000001</v>
+      </c>
+      <c r="H246" t="n">
+        <v>769.36</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="n">
+        <v>17017</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.2313</v>
+      </c>
+      <c r="D247" t="n">
+        <v>3316.99</v>
+      </c>
+      <c r="E247" t="n">
+        <v>6</v>
+      </c>
+      <c r="F247" t="n">
+        <v>104</v>
+      </c>
+      <c r="G247" t="n">
+        <v>552.83</v>
+      </c>
+      <c r="H247" t="n">
+        <v>767.22</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="n">
+        <v>12840</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="D248" t="n">
+        <v>2461.9</v>
+      </c>
+      <c r="E248" t="n">
+        <v>4</v>
+      </c>
+      <c r="F248" t="n">
+        <v>82</v>
+      </c>
+      <c r="G248" t="n">
+        <v>615.48</v>
+      </c>
+      <c r="H248" t="n">
+        <v>762.7</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="n">
+        <v>16779</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.0985</v>
+      </c>
+      <c r="D249" t="n">
+        <v>7701.66</v>
+      </c>
+      <c r="E249" t="n">
+        <v>14</v>
+      </c>
+      <c r="F249" t="n">
+        <v>63</v>
+      </c>
+      <c r="G249" t="n">
+        <v>550.12</v>
+      </c>
+      <c r="H249" t="n">
+        <v>758.61</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="n">
+        <v>17920</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.0878</v>
+      </c>
+      <c r="D250" t="n">
+        <v>8640.120000000001</v>
+      </c>
+      <c r="E250" t="n">
+        <v>16</v>
+      </c>
+      <c r="F250" t="n">
+        <v>61</v>
+      </c>
+      <c r="G250" t="n">
+        <v>540.01</v>
+      </c>
+      <c r="H250" t="n">
+        <v>758.6</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="n">
+        <v>15245</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.2121</v>
+      </c>
+      <c r="D251" t="n">
+        <v>3574.06</v>
+      </c>
+      <c r="E251" t="n">
+        <v>5</v>
+      </c>
+      <c r="F251" t="n">
+        <v>34</v>
+      </c>
+      <c r="G251" t="n">
+        <v>714.8099999999999</v>
+      </c>
+      <c r="H251" t="n">
+        <v>758.0599999999999</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="n">
+        <v>14648</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="D252" t="n">
+        <v>2858.6</v>
+      </c>
+      <c r="E252" t="n">
+        <v>7</v>
+      </c>
+      <c r="F252" t="n">
+        <v>342</v>
+      </c>
+      <c r="G252" t="n">
+        <v>408.37</v>
+      </c>
+      <c r="H252" t="n">
+        <v>757.53</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="n">
+        <v>15856</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="D253" t="n">
+        <v>9121.1</v>
+      </c>
+      <c r="E253" t="n">
+        <v>16</v>
+      </c>
+      <c r="F253" t="n">
+        <v>51</v>
+      </c>
+      <c r="G253" t="n">
+        <v>570.0700000000001</v>
+      </c>
+      <c r="H253" t="n">
+        <v>757.05</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="n">
+        <v>12806</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="D254" t="n">
+        <v>1069.5</v>
+      </c>
+      <c r="E254" t="n">
+        <v>1</v>
+      </c>
+      <c r="F254" t="n">
+        <v>488</v>
+      </c>
+      <c r="G254" t="n">
+        <v>1069.5</v>
+      </c>
+      <c r="H254" t="n">
+        <v>756.14</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="n">
+        <v>12359</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="D255" t="n">
+        <v>2499.54</v>
+      </c>
+      <c r="E255" t="n">
+        <v>4</v>
+      </c>
+      <c r="F255" t="n">
+        <v>89</v>
+      </c>
+      <c r="G255" t="n">
+        <v>624.88</v>
+      </c>
+      <c r="H255" t="n">
+        <v>755.61</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="n">
+        <v>18223</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.2431</v>
+      </c>
+      <c r="D256" t="n">
+        <v>3103.81</v>
+      </c>
+      <c r="E256" t="n">
+        <v>7</v>
+      </c>
+      <c r="F256" t="n">
+        <v>178</v>
+      </c>
+      <c r="G256" t="n">
+        <v>443.4</v>
+      </c>
+      <c r="H256" t="n">
+        <v>754.54</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="n">
+        <v>13562</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="D257" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E257" t="n">
+        <v>3</v>
+      </c>
+      <c r="F257" t="n">
+        <v>574</v>
+      </c>
+      <c r="G257" t="n">
+        <v>533.33</v>
+      </c>
+      <c r="H257" t="n">
+        <v>753.6</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="n">
+        <v>14493</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="D258" t="n">
+        <v>1389.22</v>
+      </c>
+      <c r="E258" t="n">
+        <v>2</v>
+      </c>
+      <c r="F258" t="n">
+        <v>290</v>
+      </c>
+      <c r="G258" t="n">
+        <v>694.61</v>
+      </c>
+      <c r="H258" t="n">
+        <v>751.98</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="n">
+        <v>17396</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0.1801</v>
+      </c>
+      <c r="D259" t="n">
+        <v>4173</v>
+      </c>
+      <c r="E259" t="n">
+        <v>6</v>
+      </c>
+      <c r="F259" t="n">
+        <v>48</v>
+      </c>
+      <c r="G259" t="n">
+        <v>695.5</v>
+      </c>
+      <c r="H259" t="n">
+        <v>751.5599999999999</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="n">
+        <v>15622</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0.3879</v>
+      </c>
+      <c r="D260" t="n">
+        <v>1929.7</v>
+      </c>
+      <c r="E260" t="n">
+        <v>3</v>
+      </c>
+      <c r="F260" t="n">
+        <v>125</v>
+      </c>
+      <c r="G260" t="n">
+        <v>643.23</v>
+      </c>
+      <c r="H260" t="n">
+        <v>748.53</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="n">
+        <v>13488</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.2066</v>
+      </c>
+      <c r="D261" t="n">
+        <v>3622.15</v>
+      </c>
+      <c r="E261" t="n">
+        <v>6</v>
+      </c>
+      <c r="F261" t="n">
+        <v>44</v>
+      </c>
+      <c r="G261" t="n">
+        <v>603.6900000000001</v>
+      </c>
+      <c r="H261" t="n">
+        <v>748.34</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="n">
+        <v>14933</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0.6338</v>
+      </c>
+      <c r="D262" t="n">
+        <v>1180</v>
+      </c>
+      <c r="E262" t="n">
+        <v>2</v>
+      </c>
+      <c r="F262" t="n">
+        <v>343</v>
+      </c>
+      <c r="G262" t="n">
+        <v>590</v>
+      </c>
+      <c r="H262" t="n">
+        <v>747.88</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="n">
+        <v>17850</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0.0539</v>
+      </c>
+      <c r="D263" t="n">
+        <v>13860.26</v>
+      </c>
+      <c r="E263" t="n">
+        <v>40</v>
+      </c>
+      <c r="F263" t="n">
+        <v>272</v>
+      </c>
+      <c r="G263" t="n">
+        <v>346.51</v>
+      </c>
+      <c r="H263" t="n">
+        <v>747.0700000000001</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="n">
+        <v>12533</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0.6103</v>
+      </c>
+      <c r="D264" t="n">
+        <v>1223.89</v>
+      </c>
+      <c r="E264" t="n">
+        <v>2</v>
+      </c>
+      <c r="F264" t="n">
+        <v>527</v>
+      </c>
+      <c r="G264" t="n">
+        <v>611.95</v>
+      </c>
+      <c r="H264" t="n">
+        <v>746.9400000000001</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="n">
+        <v>14088</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.2415</v>
+      </c>
+      <c r="D265" t="n">
+        <v>3092.54</v>
+      </c>
+      <c r="E265" t="n">
+        <v>5</v>
+      </c>
+      <c r="F265" t="n">
+        <v>35</v>
+      </c>
+      <c r="G265" t="n">
+        <v>618.51</v>
+      </c>
+      <c r="H265" t="n">
+        <v>746.85</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="n">
+        <v>14841</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0.2254</v>
+      </c>
+      <c r="D266" t="n">
+        <v>3313.23</v>
+      </c>
+      <c r="E266" t="n">
+        <v>6</v>
+      </c>
+      <c r="F266" t="n">
+        <v>79</v>
+      </c>
+      <c r="G266" t="n">
+        <v>552.21</v>
+      </c>
+      <c r="H266" t="n">
+        <v>746.8</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="n">
+        <v>16923</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="D267" t="n">
+        <v>3788.2</v>
+      </c>
+      <c r="E267" t="n">
+        <v>7</v>
+      </c>
+      <c r="F267" t="n">
+        <v>87</v>
+      </c>
+      <c r="G267" t="n">
+        <v>541.17</v>
+      </c>
+      <c r="H267" t="n">
+        <v>746.65</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="n">
+        <v>14855</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.6667999999999999</v>
+      </c>
+      <c r="D268" t="n">
+        <v>1117.74</v>
+      </c>
+      <c r="E268" t="n">
+        <v>1</v>
+      </c>
+      <c r="F268" t="n">
+        <v>374</v>
+      </c>
+      <c r="G268" t="n">
+        <v>1117.74</v>
+      </c>
+      <c r="H268" t="n">
+        <v>745.3099999999999</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="n">
+        <v>13692</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.6614</v>
+      </c>
+      <c r="D269" t="n">
+        <v>1125.08</v>
+      </c>
+      <c r="E269" t="n">
+        <v>1</v>
+      </c>
+      <c r="F269" t="n">
+        <v>320</v>
+      </c>
+      <c r="G269" t="n">
+        <v>1125.08</v>
+      </c>
+      <c r="H269" t="n">
+        <v>744.13</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="n">
+        <v>15384</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.5236</v>
+      </c>
+      <c r="D270" t="n">
+        <v>1412.45</v>
+      </c>
+      <c r="E270" t="n">
+        <v>2</v>
+      </c>
+      <c r="F270" t="n">
+        <v>259</v>
+      </c>
+      <c r="G270" t="n">
+        <v>706.22</v>
+      </c>
+      <c r="H270" t="n">
+        <v>739.5599999999999</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="n">
+        <v>17448</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="D271" t="n">
+        <v>4527.46</v>
+      </c>
+      <c r="E271" t="n">
+        <v>13</v>
+      </c>
+      <c r="F271" t="n">
+        <v>429</v>
+      </c>
+      <c r="G271" t="n">
+        <v>348.27</v>
+      </c>
+      <c r="H271" t="n">
+        <v>737.52</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="n">
+        <v>13756</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="D272" t="n">
+        <v>1703.11</v>
+      </c>
+      <c r="E272" t="n">
+        <v>3</v>
+      </c>
+      <c r="F272" t="n">
+        <v>285</v>
+      </c>
+      <c r="G272" t="n">
+        <v>567.7</v>
+      </c>
+      <c r="H272" t="n">
+        <v>737.45</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="n">
+        <v>13555</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.3817</v>
+      </c>
+      <c r="D273" t="n">
+        <v>1929.75</v>
+      </c>
+      <c r="E273" t="n">
+        <v>3</v>
+      </c>
+      <c r="F273" t="n">
+        <v>101</v>
+      </c>
+      <c r="G273" t="n">
+        <v>643.25</v>
+      </c>
+      <c r="H273" t="n">
+        <v>736.59</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="n">
+        <v>16200</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.4693</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1568.83</v>
+      </c>
+      <c r="E274" t="n">
+        <v>3</v>
+      </c>
+      <c r="F274" t="n">
+        <v>371</v>
+      </c>
+      <c r="G274" t="n">
+        <v>522.9400000000001</v>
+      </c>
+      <c r="H274" t="n">
+        <v>736.25</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="n">
+        <v>15353</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1982.19</v>
+      </c>
+      <c r="E275" t="n">
+        <v>4</v>
+      </c>
+      <c r="F275" t="n">
+        <v>267</v>
+      </c>
+      <c r="G275" t="n">
+        <v>495.55</v>
+      </c>
+      <c r="H275" t="n">
+        <v>735.59</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="n">
+        <v>13451</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.4407</v>
+      </c>
+      <c r="D276" t="n">
+        <v>1668.64</v>
+      </c>
+      <c r="E276" t="n">
+        <v>3</v>
+      </c>
+      <c r="F276" t="n">
+        <v>234</v>
+      </c>
+      <c r="G276" t="n">
+        <v>556.21</v>
+      </c>
+      <c r="H276" t="n">
+        <v>735.37</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="n">
+        <v>12784</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D277" t="n">
+        <v>1034.33</v>
+      </c>
+      <c r="E277" t="n">
+        <v>1</v>
+      </c>
+      <c r="F277" t="n">
+        <v>429</v>
+      </c>
+      <c r="G277" t="n">
+        <v>1034.33</v>
+      </c>
+      <c r="H277" t="n">
+        <v>734.37</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="n">
+        <v>16718</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.5769</v>
+      </c>
+      <c r="D278" t="n">
+        <v>1270.56</v>
+      </c>
+      <c r="E278" t="n">
+        <v>2</v>
+      </c>
+      <c r="F278" t="n">
+        <v>538</v>
+      </c>
+      <c r="G278" t="n">
+        <v>635.28</v>
+      </c>
+      <c r="H278" t="n">
+        <v>732.99</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="n">
+        <v>16422</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="D279" t="n">
+        <v>26351.29</v>
+      </c>
+      <c r="E279" t="n">
+        <v>36</v>
+      </c>
+      <c r="F279" t="n">
+        <v>20</v>
+      </c>
+      <c r="G279" t="n">
+        <v>731.98</v>
+      </c>
+      <c r="H279" t="n">
+        <v>732.5700000000001</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="n">
+        <v>12705</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="D280" t="n">
+        <v>1694.42</v>
+      </c>
+      <c r="E280" t="n">
+        <v>2</v>
+      </c>
+      <c r="F280" t="n">
+        <v>58</v>
+      </c>
+      <c r="G280" t="n">
+        <v>847.21</v>
+      </c>
+      <c r="H280" t="n">
+        <v>728.4299999999999</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="n">
+        <v>16398</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.6226</v>
+      </c>
+      <c r="D281" t="n">
+        <v>1169.95</v>
+      </c>
+      <c r="E281" t="n">
+        <v>1</v>
+      </c>
+      <c r="F281" t="n">
+        <v>153</v>
+      </c>
+      <c r="G281" t="n">
+        <v>1169.95</v>
+      </c>
+      <c r="H281" t="n">
+        <v>728.41</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="n">
+        <v>14256</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0.5256999999999999</v>
+      </c>
+      <c r="D282" t="n">
+        <v>1385.5</v>
+      </c>
+      <c r="E282" t="n">
+        <v>2</v>
+      </c>
+      <c r="F282" t="n">
+        <v>160</v>
+      </c>
+      <c r="G282" t="n">
+        <v>692.75</v>
+      </c>
+      <c r="H282" t="n">
+        <v>728.36</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="n">
+        <v>15674</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="D283" t="n">
+        <v>1264.28</v>
+      </c>
+      <c r="E283" t="n">
+        <v>2</v>
+      </c>
+      <c r="F283" t="n">
+        <v>552</v>
+      </c>
+      <c r="G283" t="n">
+        <v>632.14</v>
+      </c>
+      <c r="H283" t="n">
+        <v>728.23</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="n">
+        <v>14195</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="D284" t="n">
+        <v>1819.2</v>
+      </c>
+      <c r="E284" t="n">
+        <v>3</v>
+      </c>
+      <c r="F284" t="n">
+        <v>101</v>
+      </c>
+      <c r="G284" t="n">
+        <v>606.4</v>
+      </c>
+      <c r="H284" t="n">
+        <v>722.95</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="n">
+        <v>17739</v>
+      </c>
+      <c r="C285" t="n">
+        <v>0.3979</v>
+      </c>
+      <c r="D285" t="n">
+        <v>1813.53</v>
+      </c>
+      <c r="E285" t="n">
+        <v>4</v>
+      </c>
+      <c r="F285" t="n">
+        <v>260</v>
+      </c>
+      <c r="G285" t="n">
+        <v>453.38</v>
+      </c>
+      <c r="H285" t="n">
+        <v>721.6</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="n">
+        <v>14329</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="D286" t="n">
+        <v>3395.17</v>
+      </c>
+      <c r="E286" t="n">
+        <v>4</v>
+      </c>
+      <c r="F286" t="n">
+        <v>8</v>
+      </c>
+      <c r="G286" t="n">
+        <v>848.79</v>
+      </c>
+      <c r="H286" t="n">
+        <v>721.47</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="n">
+        <v>18287</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0.6702</v>
+      </c>
+      <c r="D287" t="n">
+        <v>1071.61</v>
+      </c>
+      <c r="E287" t="n">
+        <v>1</v>
+      </c>
+      <c r="F287" t="n">
+        <v>471</v>
+      </c>
+      <c r="G287" t="n">
+        <v>1071.61</v>
+      </c>
+      <c r="H287" t="n">
+        <v>718.1900000000001</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="n">
+        <v>15291</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="D288" t="n">
+        <v>2852.89</v>
+      </c>
+      <c r="E288" t="n">
+        <v>7</v>
+      </c>
+      <c r="F288" t="n">
+        <v>281</v>
+      </c>
+      <c r="G288" t="n">
+        <v>407.56</v>
+      </c>
+      <c r="H288" t="n">
+        <v>717.5</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="n">
+        <v>15570</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0.1776</v>
+      </c>
+      <c r="D289" t="n">
+        <v>4032.02</v>
+      </c>
+      <c r="E289" t="n">
+        <v>10</v>
+      </c>
+      <c r="F289" t="n">
+        <v>202</v>
+      </c>
+      <c r="G289" t="n">
+        <v>403.2</v>
+      </c>
+      <c r="H289" t="n">
+        <v>716.09</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="n">
+        <v>16894</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0.5629</v>
+      </c>
+      <c r="D290" t="n">
+        <v>1272.06</v>
+      </c>
+      <c r="E290" t="n">
+        <v>2</v>
+      </c>
+      <c r="F290" t="n">
+        <v>402</v>
+      </c>
+      <c r="G290" t="n">
+        <v>636.03</v>
+      </c>
+      <c r="H290" t="n">
+        <v>716.04</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="n">
+        <v>16843</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0.1766</v>
+      </c>
+      <c r="D291" t="n">
+        <v>4054.04</v>
+      </c>
+      <c r="E291" t="n">
+        <v>6</v>
+      </c>
+      <c r="F291" t="n">
+        <v>34</v>
+      </c>
+      <c r="G291" t="n">
+        <v>675.67</v>
+      </c>
+      <c r="H291" t="n">
+        <v>715.9400000000001</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="n">
+        <v>16746</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0.1529</v>
+      </c>
+      <c r="D292" t="n">
+        <v>4676.84</v>
+      </c>
+      <c r="E292" t="n">
+        <v>10</v>
+      </c>
+      <c r="F292" t="n">
+        <v>94</v>
+      </c>
+      <c r="G292" t="n">
+        <v>467.68</v>
+      </c>
+      <c r="H292" t="n">
+        <v>715.09</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" t="n">
+        <v>14849</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0.1892</v>
+      </c>
+      <c r="D293" t="n">
+        <v>3771.99</v>
+      </c>
+      <c r="E293" t="n">
+        <v>7</v>
+      </c>
+      <c r="F293" t="n">
+        <v>76</v>
+      </c>
+      <c r="G293" t="n">
+        <v>538.86</v>
+      </c>
+      <c r="H293" t="n">
+        <v>713.66</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="n">
+        <v>13869</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="D294" t="n">
+        <v>1639.48</v>
+      </c>
+      <c r="E294" t="n">
+        <v>3</v>
+      </c>
+      <c r="F294" t="n">
+        <v>213</v>
+      </c>
+      <c r="G294" t="n">
+        <v>546.49</v>
+      </c>
+      <c r="H294" t="n">
+        <v>713.17</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="n">
+        <v>17722</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0.6478</v>
+      </c>
+      <c r="D295" t="n">
+        <v>1096.18</v>
+      </c>
+      <c r="E295" t="n">
+        <v>1</v>
+      </c>
+      <c r="F295" t="n">
+        <v>275</v>
+      </c>
+      <c r="G295" t="n">
+        <v>1096.18</v>
+      </c>
+      <c r="H295" t="n">
+        <v>710.11</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="n">
+        <v>16053</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0.5394</v>
+      </c>
+      <c r="D296" t="n">
+        <v>1316.13</v>
+      </c>
+      <c r="E296" t="n">
+        <v>2</v>
+      </c>
+      <c r="F296" t="n">
+        <v>313</v>
+      </c>
+      <c r="G296" t="n">
+        <v>658.0599999999999</v>
+      </c>
+      <c r="H296" t="n">
+        <v>709.92</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" t="n">
+        <v>17188</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="D297" t="n">
+        <v>2219.99</v>
+      </c>
+      <c r="E297" t="n">
+        <v>5</v>
+      </c>
+      <c r="F297" t="n">
+        <v>215</v>
+      </c>
+      <c r="G297" t="n">
+        <v>444</v>
+      </c>
+      <c r="H297" t="n">
+        <v>708.62</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" t="n">
+        <v>13715</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="D298" t="n">
+        <v>2663.69</v>
+      </c>
+      <c r="E298" t="n">
+        <v>6</v>
+      </c>
+      <c r="F298" t="n">
+        <v>181</v>
+      </c>
+      <c r="G298" t="n">
+        <v>443.95</v>
+      </c>
+      <c r="H298" t="n">
+        <v>708.54</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="n">
+        <v>14235</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="D299" t="n">
+        <v>1714.96</v>
+      </c>
+      <c r="E299" t="n">
+        <v>3</v>
+      </c>
+      <c r="F299" t="n">
+        <v>160</v>
+      </c>
+      <c r="G299" t="n">
+        <v>571.65</v>
+      </c>
+      <c r="H299" t="n">
+        <v>707.42</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="n">
+        <v>16279</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="D300" t="n">
+        <v>1864.36</v>
+      </c>
+      <c r="E300" t="n">
+        <v>3</v>
+      </c>
+      <c r="F300" t="n">
+        <v>76</v>
+      </c>
+      <c r="G300" t="n">
+        <v>621.45</v>
+      </c>
+      <c r="H300" t="n">
+        <v>705.29</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="n">
+        <v>13631</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0.4616</v>
+      </c>
+      <c r="D301" t="n">
+        <v>1517.2</v>
+      </c>
+      <c r="E301" t="n">
+        <v>2</v>
+      </c>
+      <c r="F301" t="n">
+        <v>43</v>
+      </c>
+      <c r="G301" t="n">
+        <v>758.6</v>
+      </c>
+      <c r="H301" t="n">
+        <v>700.34</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H301"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/outputs/tables/00_关键结果汇总.xlsx
+++ b/outputs/tables/00_关键结果汇总.xlsx
@@ -61,8 +61,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'12b_阈值稳健性'!$A$1:$H$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'13_预测回测'!$A$1:$D$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'14_未来30天预测'!$A$1:$E$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'15_图表索引'!$A$1:$E$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'16_大屏组件'!$A$1:$C$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'15_图表索引'!$A$1:$E$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'16_大屏组件'!$A$1:$C$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'17_流失预警窗口'!$A$1:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'18_流失预警模型对比'!$A$1:$H$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'19_流失预警系数'!$A$1:$F$15</definedName>
@@ -6446,14 +6446,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="22.8" customWidth="1" min="4" max="4"/>
-    <col width="37.2" customWidth="1" min="5" max="5"/>
+    <col width="40.40000000000001" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7428,8 +7428,62 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fig36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>fig36_churn_diagnostics.png</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>业务模型图</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>M10 流失预警</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ROC（含时间外）+ 十分位流失率 + 系数方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fig37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>fig37_churn_value_scatter.png</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>业务模型图</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>M10 流失预警</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>客户价值 × 流失概率全景与预警名单定位</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E36"/>
+  <autoFilter ref="A1:E38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7440,11 +7494,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29.2" customWidth="1" min="1" max="1"/>
-    <col width="21.2" customWidth="1" min="2" max="2"/>
+    <col width="22.8" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -7618,12 +7672,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tab3_top_products</t>
+          <t>tab2_churn_decile</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOP10 热销商品</t>
+          <t>流失预警十分位区分度</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -7633,12 +7687,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tab3_cat_pie</t>
+          <t>tab2_churn_watch</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>品类结构环形图</t>
+          <t>流失预警 TOP10 名单</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -7648,72 +7702,72 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tab3_wordcloud</t>
+          <t>tab3_top_products</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>热销商品词云</t>
+          <t>TOP10 热销商品</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tab3_abc</t>
+          <t>tab3_cat_pie</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ABC 分类贡献</t>
+          <t>品类结构环形图</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tab3_rules</t>
+          <t>tab3_wordcloud</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>关联规则 Lift 排行</t>
+          <t>热销商品词云</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tab3_table</t>
+          <t>tab3_abc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>商品明细表</t>
+          <t>ABC 分类贡献</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tab4_forecast</t>
+          <t>tab3_rules</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>预测与置信区间</t>
+          <t>关联规则 Lift 排行</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -7723,12 +7777,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tab4_backtest</t>
+          <t>tab3_table</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>回测对比</t>
+          <t>商品明细表</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -7738,12 +7792,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tab4_yoy</t>
+          <t>tab4_forecast</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>同比增速复盘</t>
+          <t>预测与置信区间</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -7753,20 +7807,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tab4_bcg</t>
+          <t>tab4_backtest</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>波士顿矩阵</t>
+          <t>回测对比</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>12</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>tab4_yoy</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>同比增速复盘</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>tab4_bcg</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>波士顿矩阵</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C21"/>
+  <autoFilter ref="A1:C23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/outputs/tables/00_关键结果汇总.xlsx
+++ b/outputs/tables/00_关键结果汇总.xlsx
@@ -1068,19 +1068,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1135</v>
+        <v>996</v>
       </c>
       <c r="C2" t="n">
-        <v>4541100.09</v>
+        <v>4540111.06</v>
       </c>
       <c r="D2" t="n">
-        <v>2242989</v>
+        <v>2237736</v>
       </c>
       <c r="E2" t="n">
-        <v>22.42</v>
+        <v>22.17</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>79.98999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1334</v>
+        <v>1206</v>
       </c>
       <c r="C3" t="n">
-        <v>851399.15</v>
+        <v>852309.5600000001</v>
       </c>
       <c r="D3" t="n">
-        <v>721476</v>
+        <v>719159</v>
       </c>
       <c r="E3" t="n">
-        <v>26.35</v>
+        <v>26.84</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="4">
@@ -1112,16 +1112,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2593</v>
+        <v>2291</v>
       </c>
       <c r="C4" t="n">
-        <v>283567.53</v>
+        <v>283646.15</v>
       </c>
       <c r="D4" t="n">
-        <v>259337</v>
+        <v>266907</v>
       </c>
       <c r="E4" t="n">
-        <v>51.22</v>
+        <v>50.99</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'C': 2593, 'B': 1334, 'A': 1135}</t>
+          <t>{'C': 2291, 'B': 1206, 'A': 996}</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'A': 80.0, 'B': 15.0, 'C': 5.0}</t>
+          <t>{'A': 79.99, 'B': 15.02, 'C': 5.0}</t>
         </is>
       </c>
     </row>
